--- a/AutoBdc/py/抵押登记台账.xlsx
+++ b/AutoBdc/py/抵押登记台账.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\gitee\auto-work\AutoBdc\py\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LCY\AppData\Roaming\SPB_Data\gitee\auto-work\AutoBdc\py\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3BAF56-84B0-4746-AC47-A45ADB68DF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932B8888-7270-4A4E-9E4F-2CE2FD8561B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15900" yWindow="6870" windowWidth="22065" windowHeight="12990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13710" yWindow="3930" windowWidth="21945" windowHeight="14100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="预告抵押（合并登记）" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9970" uniqueCount="6574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9971" uniqueCount="6574">
   <si>
     <t>登记业务号</t>
   </si>
@@ -22772,7 +22772,13 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="表4" displayName="表4" ref="A1:N981" totalsRowShown="0">
-  <autoFilter ref="A1:N981" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <autoFilter ref="A1:N981" xr:uid="{00000000-0009-0000-0100-000004000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="转本登记（预告转正式）"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="登记业务号" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="抵押人1" dataDxfId="21"/>
@@ -29895,7 +29901,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="15" t="s">
         <v>502</v>
       </c>
@@ -29949,7 +29955,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="15" t="s">
         <v>513</v>
       </c>
@@ -30005,7 +30011,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="15" t="s">
         <v>521</v>
       </c>
@@ -30059,7 +30065,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="15" t="s">
         <v>530</v>
       </c>
@@ -30107,7 +30113,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="15" t="s">
         <v>537</v>
       </c>
@@ -30158,7 +30164,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="15" t="s">
         <v>545</v>
       </c>
@@ -30203,7 +30209,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="15" t="s">
         <v>551</v>
       </c>
@@ -30254,7 +30260,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="15" t="s">
         <v>559</v>
       </c>
@@ -30300,7 +30306,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="15" t="s">
         <v>567</v>
       </c>
@@ -30342,7 +30348,7 @@
         <v>曾红</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="15" t="s">
         <v>572</v>
       </c>
@@ -30384,7 +30390,7 @@
         <v>郭宁</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="15" t="s">
         <v>577</v>
       </c>
@@ -30432,7 +30438,7 @@
         <v>胡红英 李章仁</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="15" t="s">
         <v>584</v>
       </c>
@@ -30474,7 +30480,7 @@
         <v>康艳梅</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="15" t="s">
         <v>589</v>
       </c>
@@ -30516,7 +30522,7 @@
         <v>王倩</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="15" t="s">
         <v>594</v>
       </c>
@@ -30564,7 +30570,7 @@
         <v>邹琅 赖平平</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:19" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="15" t="s">
         <v>601</v>
       </c>
@@ -30606,7 +30612,7 @@
         <v>匡仁棒</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="15" t="s">
         <v>607</v>
       </c>
@@ -30654,7 +30660,7 @@
         <v>刘志蓉 刘建忠</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="15" t="s">
         <v>614</v>
       </c>
@@ -30702,7 +30708,7 @@
         <v>谢志刚 范兰</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="15" t="s">
         <v>621</v>
       </c>
@@ -30744,7 +30750,7 @@
         <v>戴莹</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="15" t="s">
         <v>626</v>
       </c>
@@ -30786,7 +30792,7 @@
         <v>郭奇智</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="15" t="s">
         <v>631</v>
       </c>
@@ -30834,7 +30840,7 @@
         <v>郭晓倩 曾圣皆</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="15" t="s">
         <v>638</v>
       </c>
@@ -30882,7 +30888,7 @@
         <v>周军平 廖玉香</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
         <v>645</v>
       </c>
@@ -30930,7 +30936,7 @@
         <v>孙丽娟 唐斌</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="15" t="s">
         <v>652</v>
       </c>
@@ -30978,7 +30984,7 @@
         <v>刘玲 周九羊</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="15" t="s">
         <v>659</v>
       </c>
@@ -31026,7 +31032,7 @@
         <v>夏晓敏 宋春英</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="15" t="s">
         <v>666</v>
       </c>
@@ -31068,7 +31074,7 @@
         <v>巫秋月</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="15" t="s">
         <v>671</v>
       </c>
@@ -31110,7 +31116,7 @@
         <v>杨美琴</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="15" t="s">
         <v>676</v>
       </c>
@@ -31158,7 +31164,7 @@
         <v>郭红梅 陈立军</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="15" t="s">
         <v>683</v>
       </c>
@@ -31206,7 +31212,7 @@
         <v>周庆初 罗林林</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="15" t="s">
         <v>690</v>
       </c>
@@ -31254,7 +31260,7 @@
         <v>罗吉祥 张丹</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="15" t="s">
         <v>697</v>
       </c>
@@ -31302,7 +31308,7 @@
         <v>曾爱萍 张莉花</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="15" t="s">
         <v>704</v>
       </c>
@@ -31350,7 +31356,7 @@
         <v>王小丁 肖有志</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="15" t="s">
         <v>711</v>
       </c>
@@ -31398,7 +31404,7 @@
         <v>周志强 姜语</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="15" t="s">
         <v>718</v>
       </c>
@@ -31440,7 +31446,7 @@
         <v>朱博琨</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="15" t="s">
         <v>723</v>
       </c>
@@ -31488,7 +31494,7 @@
         <v>晏勇 廖彩琴</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="15" t="s">
         <v>730</v>
       </c>
@@ -31536,7 +31542,7 @@
         <v>黄先庆 黄翠</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="15" t="s">
         <v>737</v>
       </c>
@@ -31584,7 +31590,7 @@
         <v>宁淑娟 曾勇辉</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="15" t="s">
         <v>744</v>
       </c>
@@ -31626,7 +31632,7 @@
         <v>刘翰阳</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="15" t="s">
         <v>749</v>
       </c>
@@ -31674,7 +31680,7 @@
         <v>罗桃根 赖露萍</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="15" t="s">
         <v>756</v>
       </c>
@@ -31716,7 +31722,7 @@
         <v>张益</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="15" t="s">
         <v>762</v>
       </c>
@@ -31764,7 +31770,7 @@
         <v>黄称龙 罗海珍</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="15" t="s">
         <v>769</v>
       </c>
@@ -31812,7 +31818,7 @@
         <v>周文宏 吴快乐</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="15" t="s">
         <v>776</v>
       </c>
@@ -31860,7 +31866,7 @@
         <v>朱适誉 盛水兵</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="15" t="s">
         <v>783</v>
       </c>
@@ -31908,7 +31914,7 @@
         <v>虞永梅 李良启</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="15" t="s">
         <v>790</v>
       </c>
@@ -31956,7 +31962,7 @@
         <v>王星 周萍华</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="15" t="s">
         <v>797</v>
       </c>
@@ -31998,7 +32004,7 @@
         <v>张建金</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="15" t="s">
         <v>802</v>
       </c>
@@ -32040,7 +32046,7 @@
         <v>邓炳秀</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="15" t="s">
         <v>807</v>
       </c>
@@ -32088,7 +32094,7 @@
         <v>邓卫平 廖昔君</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="15" t="s">
         <v>814</v>
       </c>
@@ -32130,7 +32136,7 @@
         <v>李丽丹</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="15" t="s">
         <v>820</v>
       </c>
@@ -32178,7 +32184,7 @@
         <v>陈秋平 杨学苗</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="15" t="s">
         <v>827</v>
       </c>
@@ -32226,7 +32232,7 @@
         <v>朱晓辉 陈志鑫</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="15" t="s">
         <v>834</v>
       </c>
@@ -32268,7 +32274,7 @@
         <v>周小飞</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="15" t="s">
         <v>839</v>
       </c>
@@ -32316,7 +32322,7 @@
         <v>张高桂 李龙飞</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="15" t="s">
         <v>846</v>
       </c>
@@ -32364,7 +32370,7 @@
         <v>戴彬 邓晓燕</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="15" t="s">
         <v>853</v>
       </c>
@@ -32412,7 +32418,7 @@
         <v>黄月兰 王昭云</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="15" t="s">
         <v>860</v>
       </c>
@@ -32460,7 +32466,7 @@
         <v>戴林堂 王江苹</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="15" t="s">
         <v>868</v>
       </c>
@@ -32508,7 +32514,7 @@
         <v>谢云 肖勇水</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="15" t="s">
         <v>875</v>
       </c>
@@ -32556,7 +32562,7 @@
         <v>罗涛 郭清清</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="15" t="s">
         <v>882</v>
       </c>
@@ -32602,7 +32608,7 @@
         <v>杨晨 刘玲</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="15" t="s">
         <v>888</v>
       </c>
@@ -32644,7 +32650,7 @@
         <v>王万超</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="15" t="s">
         <v>894</v>
       </c>
@@ -32692,7 +32698,7 @@
         <v>夏侯佐迩 何燕</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="15" t="s">
         <v>901</v>
       </c>
@@ -32734,7 +32740,7 @@
         <v>欧阳回清</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="15" t="s">
         <v>907</v>
       </c>
@@ -32776,7 +32782,7 @@
         <v>罗富勇</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="15" t="s">
         <v>912</v>
       </c>
@@ -32870,7 +32876,7 @@
         <v>周六姑 刘足华</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="15" t="s">
         <v>921</v>
       </c>
@@ -32918,7 +32924,7 @@
         <v>吴桂花 吴维立</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="15" t="s">
         <v>928</v>
       </c>
@@ -32966,7 +32972,7 @@
         <v>肖文星 王龙</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="15" t="s">
         <v>935</v>
       </c>
@@ -33014,7 +33020,7 @@
         <v>梁崇焕 郭星</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="15" t="s">
         <v>942</v>
       </c>
@@ -33056,7 +33062,7 @@
         <v>熊春妹</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="15" t="s">
         <v>947</v>
       </c>
@@ -33104,7 +33110,7 @@
         <v>罗跃华 王春兰</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="15" t="s">
         <v>954</v>
       </c>
@@ -33146,7 +33152,7 @@
         <v>杨文清</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="15" t="s">
         <v>960</v>
       </c>
@@ -33182,7 +33188,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="15" t="s">
         <v>964</v>
       </c>
@@ -33230,7 +33236,7 @@
         <v>朱小兵 郭月媛</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="15" t="s">
         <v>971</v>
       </c>
@@ -33270,7 +33276,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="15" t="s">
         <v>977</v>
       </c>
@@ -33318,7 +33324,7 @@
         <v>钟姗姗 张汉清</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="15" t="s">
         <v>984</v>
       </c>
@@ -33366,7 +33372,7 @@
         <v>何居贵 杨香兰 何显照</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="15" t="s">
         <v>992</v>
       </c>
@@ -33414,7 +33420,7 @@
         <v>黎凤 李卫</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="15" t="s">
         <v>999</v>
       </c>
@@ -33462,7 +33468,7 @@
         <v>管美玲 旷有博</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="15" t="s">
         <v>1006</v>
       </c>
@@ -33500,7 +33506,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="15" t="s">
         <v>1011</v>
       </c>
@@ -33540,7 +33546,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="15" t="s">
         <v>1017</v>
       </c>
@@ -33580,7 +33586,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="15" t="s">
         <v>1023</v>
       </c>
@@ -33620,7 +33626,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="15" t="s">
         <v>1029</v>
       </c>
@@ -33660,7 +33666,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="15" t="s">
         <v>1035</v>
       </c>
@@ -33708,7 +33714,7 @@
         <v>王强 潘洋琼</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="15" t="s">
         <v>1043</v>
       </c>
@@ -33750,7 +33756,7 @@
         <v>刘星</v>
       </c>
     </row>
-    <row r="86" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="15" t="s">
         <v>1048</v>
       </c>
@@ -33796,7 +33802,7 @@
         <v>黄嫩 周毅</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="15" t="s">
         <v>1055</v>
       </c>
@@ -33836,7 +33842,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15" t="s">
         <v>1061</v>
       </c>
@@ -33876,7 +33882,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="15" t="s">
         <v>1067</v>
       </c>
@@ -33916,7 +33922,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="15" t="s">
         <v>1073</v>
       </c>
@@ -33964,7 +33970,7 @@
         <v>杨黎君 罗惟银</v>
       </c>
     </row>
-    <row r="91" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="15" t="s">
         <v>1077</v>
       </c>
@@ -34004,7 +34010,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="15" t="s">
         <v>1083</v>
       </c>
@@ -34042,7 +34048,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="15" t="s">
         <v>1089</v>
       </c>
@@ -34090,7 +34096,7 @@
         <v>刘佳丽 曾建</v>
       </c>
     </row>
-    <row r="94" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="15" t="s">
         <v>1096</v>
       </c>
@@ -34132,7 +34138,7 @@
         <v>彭婧</v>
       </c>
     </row>
-    <row r="95" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="15" t="s">
         <v>1101</v>
       </c>
@@ -34174,7 +34180,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="15" t="s">
         <v>1107</v>
       </c>
@@ -34214,7 +34220,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="15" t="s">
         <v>1113</v>
       </c>
@@ -34262,7 +34268,7 @@
         <v>杨浪开 肖清花</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="15" t="s">
         <v>1115</v>
       </c>
@@ -34310,7 +34316,7 @@
         <v>蒋妍妮 郭君明</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="15" t="s">
         <v>1122</v>
       </c>
@@ -34358,7 +34364,7 @@
         <v>高永玲 李艳</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="15" t="s">
         <v>1129</v>
       </c>
@@ -34398,7 +34404,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="15" t="s">
         <v>1135</v>
       </c>
@@ -34440,7 +34446,7 @@
         <v>王朋英</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="15" t="s">
         <v>1140</v>
       </c>
@@ -34482,7 +34488,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="15" t="s">
         <v>1146</v>
       </c>
@@ -34518,7 +34524,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="15" t="s">
         <v>1150</v>
       </c>
@@ -34558,7 +34564,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="15" t="s">
         <v>1156</v>
       </c>
@@ -34598,7 +34604,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="15" t="s">
         <v>1162</v>
       </c>
@@ -34638,7 +34644,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="15" t="s">
         <v>1168</v>
       </c>
@@ -34674,7 +34680,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="15" t="s">
         <v>1172</v>
       </c>
@@ -34714,7 +34720,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="15" t="s">
         <v>1178</v>
       </c>
@@ -34754,7 +34760,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="15" t="s">
         <v>1184</v>
       </c>
@@ -34794,7 +34800,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="15" t="s">
         <v>1190</v>
       </c>
@@ -34834,7 +34840,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="15" t="s">
         <v>1196</v>
       </c>
@@ -34870,7 +34876,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="15" t="s">
         <v>1200</v>
       </c>
@@ -34906,7 +34912,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="15" t="s">
         <v>1204</v>
       </c>
@@ -34942,7 +34948,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="15" t="s">
         <v>1208</v>
       </c>
@@ -34982,7 +34988,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="15" t="s">
         <v>1213</v>
       </c>
@@ -35016,7 +35022,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="15" t="s">
         <v>1217</v>
       </c>
@@ -35058,7 +35064,7 @@
         <v>喻敏</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="15" t="s">
         <v>1222</v>
       </c>
@@ -35100,7 +35106,7 @@
         <v>周宏华</v>
       </c>
     </row>
-    <row r="119" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="15" t="s">
         <v>1227</v>
       </c>
@@ -35142,7 +35148,7 @@
         <v>肖蒙恩</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="15" t="s">
         <v>1233</v>
       </c>
@@ -35182,7 +35188,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="15" t="s">
         <v>1239</v>
       </c>
@@ -35218,7 +35224,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="15" t="s">
         <v>1242</v>
       </c>
@@ -35258,7 +35264,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="15" t="s">
         <v>1248</v>
       </c>
@@ -35294,7 +35300,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="15" t="s">
         <v>1252</v>
       </c>
@@ -35334,7 +35340,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="15" t="s">
         <v>1258</v>
       </c>
@@ -35382,7 +35388,7 @@
         <v>吴花秀 范观音</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="15" t="s">
         <v>1265</v>
       </c>
@@ -35430,7 +35436,7 @@
         <v>刘晶 余刚</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="15" t="s">
         <v>1272</v>
       </c>
@@ -35472,7 +35478,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="15" t="s">
         <v>1279</v>
       </c>
@@ -35520,7 +35526,7 @@
         <v>王红平 宋润秀</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="15" t="s">
         <v>1286</v>
       </c>
@@ -35562,7 +35568,7 @@
         <v>徐燕</v>
       </c>
     </row>
-    <row r="130" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="15" t="s">
         <v>1291</v>
       </c>
@@ -35610,7 +35616,7 @@
         <v>肖祖烈 王美香</v>
       </c>
     </row>
-    <row r="131" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="15" t="s">
         <v>1298</v>
       </c>
@@ -35658,7 +35664,7 @@
         <v>章荣杰 黄冬兰</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="15" t="s">
         <v>1301</v>
       </c>
@@ -35706,7 +35712,7 @@
         <v>王林非 秦文确</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="15" t="s">
         <v>1308</v>
       </c>
@@ -35754,7 +35760,7 @@
         <v>刘青 朱梦杨</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="15" t="s">
         <v>1315</v>
       </c>
@@ -35794,7 +35800,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="15" t="s">
         <v>1321</v>
       </c>
@@ -35836,7 +35842,7 @@
         <v>李菊香</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="15" t="s">
         <v>1326</v>
       </c>
@@ -35878,7 +35884,7 @@
         <v>李智寿</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="15" t="s">
         <v>1331</v>
       </c>
@@ -35914,7 +35920,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="15" t="s">
         <v>1335</v>
       </c>
@@ -35954,7 +35960,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="15" t="s">
         <v>1342</v>
       </c>
@@ -35994,7 +36000,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="15" t="s">
         <v>1348</v>
       </c>
@@ -36034,7 +36040,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="15" t="s">
         <v>1354</v>
       </c>
@@ -36074,7 +36080,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="15" t="s">
         <v>1360</v>
       </c>
@@ -36110,7 +36116,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="15" t="s">
         <v>1364</v>
       </c>
@@ -36158,7 +36164,7 @@
         <v>李招华 王其光</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="15" t="s">
         <v>1371</v>
       </c>
@@ -36194,7 +36200,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="15" t="s">
         <v>1375</v>
       </c>
@@ -36230,7 +36236,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="15" t="s">
         <v>1379</v>
       </c>
@@ -36266,7 +36272,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="15" t="s">
         <v>1381</v>
       </c>
@@ -36308,7 +36314,7 @@
         <v>李媛媛</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="15" t="s">
         <v>1386</v>
       </c>
@@ -36344,7 +36350,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="15" t="s">
         <v>1390</v>
       </c>
@@ -36386,7 +36392,7 @@
         <v>郭亮</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="15" t="s">
         <v>1392</v>
       </c>
@@ -36434,7 +36440,7 @@
         <v>吴海庆 罗金珍</v>
       </c>
     </row>
-    <row r="151" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="15" t="s">
         <v>1399</v>
       </c>
@@ -36482,7 +36488,7 @@
         <v>陈小娥 朱禄文</v>
       </c>
     </row>
-    <row r="152" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="15" t="s">
         <v>1406</v>
       </c>
@@ -36530,7 +36536,7 @@
         <v>曾小明 何宝玲</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="15" t="s">
         <v>1413</v>
       </c>
@@ -36570,7 +36576,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="15" t="s">
         <v>1419</v>
       </c>
@@ -36618,7 +36624,7 @@
         <v>郭洁洁 贺其铮</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="15" t="s">
         <v>1426</v>
       </c>
@@ -36660,7 +36666,7 @@
         <v>郭坎</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="15" t="s">
         <v>1431</v>
       </c>
@@ -36706,7 +36712,7 @@
         <v>孙小勇 刘秋莲</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="15" t="s">
         <v>1438</v>
       </c>
@@ -36754,7 +36760,7 @@
         <v>何丹 崔勇</v>
       </c>
     </row>
-    <row r="158" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="15" t="s">
         <v>1445</v>
       </c>
@@ -36802,7 +36808,7 @@
         <v>万云强 刘兰</v>
       </c>
     </row>
-    <row r="159" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="15" t="s">
         <v>1447</v>
       </c>
@@ -36838,7 +36844,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="15" t="s">
         <v>1451</v>
       </c>
@@ -36878,7 +36884,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="15" t="s">
         <v>1457</v>
       </c>
@@ -36918,7 +36924,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="15" t="s">
         <v>1463</v>
       </c>
@@ -36954,7 +36960,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="15" t="s">
         <v>1467</v>
       </c>
@@ -36994,7 +37000,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="15" t="s">
         <v>1473</v>
       </c>
@@ -37032,7 +37038,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="15" t="s">
         <v>1478</v>
       </c>
@@ -37068,7 +37074,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="15" t="s">
         <v>1482</v>
       </c>
@@ -37108,7 +37114,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="15" t="s">
         <v>1488</v>
       </c>
@@ -37144,7 +37150,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="15" t="s">
         <v>1492</v>
       </c>
@@ -37190,7 +37196,7 @@
         <v>李渊 周媛华</v>
       </c>
     </row>
-    <row r="169" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="15" t="s">
         <v>1499</v>
       </c>
@@ -37236,7 +37242,7 @@
         <v>郭敏 曾志清</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="15" t="s">
         <v>1506</v>
       </c>
@@ -37278,7 +37284,7 @@
         <v>郭芮彤</v>
       </c>
     </row>
-    <row r="171" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="15" t="s">
         <v>1511</v>
       </c>
@@ -37318,7 +37324,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="15" t="s">
         <v>1517</v>
       </c>
@@ -37358,7 +37364,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="15" t="s">
         <v>1523</v>
       </c>
@@ -37444,7 +37450,7 @@
         <v>周小勇 杨珍丽</v>
       </c>
     </row>
-    <row r="175" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="15" t="s">
         <v>1532</v>
       </c>
@@ -37484,7 +37490,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="15" t="s">
         <v>1538</v>
       </c>
@@ -37524,7 +37530,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="15" t="s">
         <v>1544</v>
       </c>
@@ -37560,7 +37566,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="15" t="s">
         <v>1548</v>
       </c>
@@ -37600,7 +37606,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="15" t="s">
         <v>1554</v>
       </c>
@@ -37640,7 +37646,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="15" t="s">
         <v>1560</v>
       </c>
@@ -37676,7 +37682,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="15" t="s">
         <v>1564</v>
       </c>
@@ -37712,7 +37718,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="15" t="s">
         <v>1568</v>
       </c>
@@ -37752,7 +37758,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="15" t="s">
         <v>1574</v>
       </c>
@@ -37796,7 +37802,7 @@
         <v>刘桂林 刘琼</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="15" t="s">
         <v>1581</v>
       </c>
@@ -37884,7 +37890,7 @@
         <v>王纯有 郭小红</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="15" t="s">
         <v>1595</v>
       </c>
@@ -37928,7 +37934,7 @@
         <v>吴才旺 吴莉</v>
       </c>
     </row>
-    <row r="187" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="15" t="s">
         <v>1602</v>
       </c>
@@ -37976,7 +37982,7 @@
         <v>姚通 范淑慧</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="15" t="s">
         <v>1604</v>
       </c>
@@ -38016,7 +38022,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="15" t="s">
         <v>1610</v>
       </c>
@@ -38064,7 +38070,7 @@
         <v>曾安邦 郭安珍</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="15" t="s">
         <v>1617</v>
       </c>
@@ -38112,7 +38118,7 @@
         <v>赖红梅 胡青</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="15" t="s">
         <v>1624</v>
       </c>
@@ -38158,7 +38164,7 @@
         <v>杨菊蓉 郭春亮</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="15" t="s">
         <v>1631</v>
       </c>
@@ -38196,7 +38202,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="15" t="s">
         <v>1636</v>
       </c>
@@ -38238,7 +38244,7 @@
         <v>钟恩华</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="15" t="s">
         <v>1642</v>
       </c>
@@ -38274,7 +38280,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="15" t="s">
         <v>1646</v>
       </c>
@@ -38314,7 +38320,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="15" t="s">
         <v>1652</v>
       </c>
@@ -38354,7 +38360,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="15" t="s">
         <v>1658</v>
       </c>
@@ -38390,7 +38396,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="15" t="s">
         <v>1662</v>
       </c>
@@ -38430,7 +38436,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="15" t="s">
         <v>1668</v>
       </c>
@@ -38468,7 +38474,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="15" t="s">
         <v>1673</v>
       </c>
@@ -38504,7 +38510,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="15" t="s">
         <v>1677</v>
       </c>
@@ -38544,7 +38550,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="15" t="s">
         <v>1683</v>
       </c>
@@ -38588,7 +38594,7 @@
         <v>温火丽 彭宁斌</v>
       </c>
     </row>
-    <row r="203" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="15" t="s">
         <v>1690</v>
       </c>
@@ -38636,7 +38642,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="204" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="15" t="s">
         <v>1693</v>
       </c>
@@ -38684,7 +38690,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="205" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="15" t="s">
         <v>1695</v>
       </c>
@@ -38732,7 +38738,7 @@
         <v>罗春华 袁淑珍</v>
       </c>
     </row>
-    <row r="206" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="15" t="s">
         <v>1697</v>
       </c>
@@ -38768,7 +38774,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="15" t="s">
         <v>1701</v>
       </c>
@@ -38812,7 +38818,7 @@
         <v>张晓龙 周彤彤</v>
       </c>
     </row>
-    <row r="208" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="15" t="s">
         <v>1708</v>
       </c>
@@ -38854,7 +38860,7 @@
         <v/>
       </c>
     </row>
-    <row r="209" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="15" t="s">
         <v>1714</v>
       </c>
@@ -38896,7 +38902,7 @@
         <v>刘文涛</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="15" t="s">
         <v>1719</v>
       </c>
@@ -38936,7 +38942,7 @@
         <v/>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="15" t="s">
         <v>1725</v>
       </c>
@@ -38982,7 +38988,7 @@
         <v>龙轩 刘华美</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="15" t="s">
         <v>1732</v>
       </c>
@@ -39030,7 +39036,7 @@
         <v>郭必塬 彭小妹</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="15" t="s">
         <v>1739</v>
       </c>
@@ -39074,7 +39080,7 @@
         <v>曾昭君 陈曦</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="15" t="s">
         <v>1746</v>
       </c>
@@ -39116,7 +39122,7 @@
         <v>罗小花</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="15" t="s">
         <v>1751</v>
       </c>
@@ -39164,7 +39170,7 @@
         <v>曾洪 卢江华</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="15" t="s">
         <v>1754</v>
       </c>
@@ -39210,7 +39216,7 @@
         <v>蒋兰华 陈国华</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="18" t="s">
         <v>1757</v>
       </c>
@@ -39258,7 +39264,7 @@
         <v>曹胜智 谢雪峰</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="15" t="s">
         <v>1764</v>
       </c>
@@ -39298,7 +39304,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="15" t="s">
         <v>1770</v>
       </c>
@@ -39338,7 +39344,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="15" t="s">
         <v>1776</v>
       </c>
@@ -39380,7 +39386,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="15" t="s">
         <v>1777</v>
       </c>
@@ -39420,7 +39426,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="15" t="s">
         <v>1783</v>
       </c>
@@ -39456,7 +39462,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="15" t="s">
         <v>1787</v>
       </c>
@@ -39502,7 +39508,7 @@
         <v>毛智文 杜玉梅</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="15" t="s">
         <v>1794</v>
       </c>
@@ -39544,7 +39550,7 @@
         <v>熊丹琪</v>
       </c>
     </row>
-    <row r="225" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="15" t="s">
         <v>1799</v>
       </c>
@@ -39580,7 +39586,7 @@
         <v/>
       </c>
     </row>
-    <row r="226" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="15" t="s">
         <v>1803</v>
       </c>
@@ -39628,7 +39634,7 @@
         <v>何文祥 吴芳</v>
       </c>
     </row>
-    <row r="227" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="15" t="s">
         <v>1810</v>
       </c>
@@ -39676,7 +39682,7 @@
         <v>陈仕斌 肖琼</v>
       </c>
     </row>
-    <row r="228" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="15" t="s">
         <v>1817</v>
       </c>
@@ -39718,7 +39724,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="15" t="s">
         <v>1823</v>
       </c>
@@ -39758,7 +39764,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="15" t="s">
         <v>1829</v>
       </c>
@@ -39798,7 +39804,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="15" t="s">
         <v>1835</v>
       </c>
@@ -39834,7 +39840,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="15" t="s">
         <v>1838</v>
       </c>
@@ -39874,7 +39880,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="15" t="s">
         <v>1844</v>
       </c>
@@ -39912,7 +39918,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="15" t="s">
         <v>1849</v>
       </c>
@@ -39950,7 +39956,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="15" t="s">
         <v>1854</v>
       </c>
@@ -39992,7 +39998,7 @@
         <v>李伊丽</v>
       </c>
     </row>
-    <row r="236" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="15" t="s">
         <v>1859</v>
       </c>
@@ -40038,7 +40044,7 @@
         <v>尚娟 贺勇华</v>
       </c>
     </row>
-    <row r="237" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="6" t="s">
         <v>1866</v>
       </c>
@@ -40076,7 +40082,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="15" t="s">
         <v>1871</v>
       </c>
@@ -40112,7 +40118,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="15" t="s">
         <v>1875</v>
       </c>
@@ -40188,7 +40194,7 @@
         <v>李丹</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="15" t="s">
         <v>1885</v>
       </c>
@@ -40228,7 +40234,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="15" t="s">
         <v>1891</v>
       </c>
@@ -40268,7 +40274,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="15" t="s">
         <v>1897</v>
       </c>
@@ -40304,7 +40310,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="15" t="s">
         <v>1901</v>
       </c>
@@ -40340,7 +40346,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="15" t="s">
         <v>1905</v>
       </c>
@@ -40382,7 +40388,7 @@
         <v>彭钟华</v>
       </c>
     </row>
-    <row r="246" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="15" t="s">
         <v>1910</v>
       </c>
@@ -40428,7 +40434,7 @@
         <v>田小洋 曹金红</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="15" t="s">
         <v>1912</v>
       </c>
@@ -40474,7 +40480,7 @@
         <v>肖敏华 刘文斌</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="15" t="s">
         <v>1919</v>
       </c>
@@ -40516,7 +40522,7 @@
         <v>曾圣堪</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="15" t="s">
         <v>1924</v>
       </c>
@@ -40562,7 +40568,7 @@
         <v>张紫薇 钟恩华</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="15" t="s">
         <v>1929</v>
       </c>
@@ -40604,7 +40610,7 @@
         <v>徐丽</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="15" t="s">
         <v>1934</v>
       </c>
@@ -40646,7 +40652,7 @@
         <v>范孝兴</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="15" t="s">
         <v>1939</v>
       </c>
@@ -40694,7 +40700,7 @@
         <v>刘红梅 王建勇</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="15" t="s">
         <v>1946</v>
       </c>
@@ -40736,7 +40742,7 @@
         <v>欧阳思</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="15" t="s">
         <v>1951</v>
       </c>
@@ -40778,7 +40784,7 @@
         <v>朱志勇</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="15" t="s">
         <v>1956</v>
       </c>
@@ -40866,7 +40872,7 @@
         <v>杨凤飞</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="15" t="s">
         <v>1968</v>
       </c>
@@ -40914,7 +40920,7 @@
         <v>肖明坊 曾小娟</v>
       </c>
     </row>
-    <row r="258" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="15" t="s">
         <v>1975</v>
       </c>
@@ -40956,7 +40962,7 @@
         <v>曾凡曦</v>
       </c>
     </row>
-    <row r="259" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="15" t="s">
         <v>1980</v>
       </c>
@@ -41004,7 +41010,7 @@
         <v>朱亚玲 赖平洋</v>
       </c>
     </row>
-    <row r="260" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="15" t="s">
         <v>1987</v>
       </c>
@@ -41052,7 +41058,7 @@
         <v>李刚 阮丽琼</v>
       </c>
     </row>
-    <row r="261" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="15" t="s">
         <v>1994</v>
       </c>
@@ -41092,7 +41098,7 @@
         <v>徐子豪</v>
       </c>
     </row>
-    <row r="262" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="15" t="s">
         <v>1999</v>
       </c>
@@ -41126,7 +41132,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="15" t="s">
         <v>2003</v>
       </c>
@@ -41168,7 +41174,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="15" t="s">
         <v>2009</v>
       </c>
@@ -41208,7 +41214,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="15" t="s">
         <v>2015</v>
       </c>
@@ -41244,7 +41250,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="15" t="s">
         <v>2019</v>
       </c>
@@ -41284,7 +41290,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="15" t="s">
         <v>2025</v>
       </c>
@@ -41330,7 +41336,7 @@
         <v>曾美琴 郭聪聪</v>
       </c>
     </row>
-    <row r="268" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="15" t="s">
         <v>2032</v>
       </c>
@@ -41370,7 +41376,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="15" t="s">
         <v>2033</v>
       </c>
@@ -41410,7 +41416,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="15" t="s">
         <v>2039</v>
       </c>
@@ -41446,7 +41452,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="15" t="s">
         <v>2043</v>
       </c>
@@ -41486,7 +41492,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="15" t="s">
         <v>2049</v>
       </c>
@@ -41526,7 +41532,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="15" t="s">
         <v>2055</v>
       </c>
@@ -41566,7 +41572,7 @@
         <v>裴超元</v>
       </c>
     </row>
-    <row r="274" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="15" t="s">
         <v>2060</v>
       </c>
@@ -41614,7 +41620,7 @@
         <v>刘辛蔚 许伟梅</v>
       </c>
     </row>
-    <row r="275" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="15" t="s">
         <v>2067</v>
       </c>
@@ -41662,7 +41668,7 @@
         <v>周丽萍 邱礼水</v>
       </c>
     </row>
-    <row r="276" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="15" t="s">
         <v>2074</v>
       </c>
@@ -41708,7 +41714,7 @@
         <v>欧阳珍珠 王小坤</v>
       </c>
     </row>
-    <row r="277" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="15" t="s">
         <v>2081</v>
       </c>
@@ -41750,7 +41756,7 @@
         <v>魏丽萍</v>
       </c>
     </row>
-    <row r="278" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="15" t="s">
         <v>2083</v>
       </c>
@@ -41792,7 +41798,7 @@
         <v>曾宪福</v>
       </c>
     </row>
-    <row r="279" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="15" t="s">
         <v>2088</v>
       </c>
@@ -41826,7 +41832,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="15" t="s">
         <v>2091</v>
       </c>
@@ -41866,7 +41872,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="15" t="s">
         <v>2097</v>
       </c>
@@ -41906,7 +41912,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="15" t="s">
         <v>2103</v>
       </c>
@@ -41946,7 +41952,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="15" t="s">
         <v>2109</v>
       </c>
@@ -41986,7 +41992,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="15" t="s">
         <v>2115</v>
       </c>
@@ -42024,7 +42030,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="15" t="s">
         <v>2120</v>
       </c>
@@ -42064,7 +42070,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="15" t="s">
         <v>2126</v>
       </c>
@@ -42106,7 +42112,7 @@
         <v>宋茜</v>
       </c>
     </row>
-    <row r="287" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="15" t="s">
         <v>2131</v>
       </c>
@@ -42272,7 +42278,7 @@
         <v>刘文文</v>
       </c>
     </row>
-    <row r="291" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="15" t="s">
         <v>2153</v>
       </c>
@@ -42314,7 +42320,7 @@
         <v>陈忠财</v>
       </c>
     </row>
-    <row r="292" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="15" t="s">
         <v>2158</v>
       </c>
@@ -42354,7 +42360,7 @@
         <v>肖惠霞</v>
       </c>
     </row>
-    <row r="293" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="15" t="s">
         <v>2163</v>
       </c>
@@ -42398,7 +42404,7 @@
         <v>晏元昌 晏志远</v>
       </c>
     </row>
-    <row r="294" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="15" t="s">
         <v>2170</v>
       </c>
@@ -42446,7 +42452,7 @@
         <v>丘日先 刘招玉</v>
       </c>
     </row>
-    <row r="295" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="15" t="s">
         <v>2177</v>
       </c>
@@ -42482,7 +42488,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="15" t="s">
         <v>2181</v>
       </c>
@@ -42518,7 +42524,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="15" t="s">
         <v>2185</v>
       </c>
@@ -42564,7 +42570,7 @@
         <v>刘彦 王芬</v>
       </c>
     </row>
-    <row r="298" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="15" t="s">
         <v>2192</v>
       </c>
@@ -42612,7 +42618,7 @@
         <v>李章银 陈娟</v>
       </c>
     </row>
-    <row r="299" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="15" t="s">
         <v>2199</v>
       </c>
@@ -42660,7 +42666,7 @@
         <v>李安军 刘正华</v>
       </c>
     </row>
-    <row r="300" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="15" t="s">
         <v>2207</v>
       </c>
@@ -42702,7 +42708,7 @@
         <v>龚剑</v>
       </c>
     </row>
-    <row r="301" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="15" t="s">
         <v>2212</v>
       </c>
@@ -42742,7 +42748,7 @@
         <v>王翀</v>
       </c>
     </row>
-    <row r="302" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="15" t="s">
         <v>2217</v>
       </c>
@@ -42786,7 +42792,7 @@
         <v>田莉 彭彪平</v>
       </c>
     </row>
-    <row r="303" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="15" t="s">
         <v>2224</v>
       </c>
@@ -42826,7 +42832,7 @@
         <v>王春梅</v>
       </c>
     </row>
-    <row r="304" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="15" t="s">
         <v>2229</v>
       </c>
@@ -42874,7 +42880,7 @@
         <v>王斌斋 黄琴</v>
       </c>
     </row>
-    <row r="305" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="15" t="s">
         <v>2236</v>
       </c>
@@ -42910,7 +42916,7 @@
         <v/>
       </c>
     </row>
-    <row r="306" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="15" t="s">
         <v>2241</v>
       </c>
@@ -42956,7 +42962,7 @@
         <v>胡凤明 朱青凤</v>
       </c>
     </row>
-    <row r="307" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="15" t="s">
         <v>2248</v>
       </c>
@@ -43000,7 +43006,7 @@
         <v>刘可文 罗艳红</v>
       </c>
     </row>
-    <row r="308" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="15" t="s">
         <v>2255</v>
       </c>
@@ -43042,7 +43048,7 @@
         <v>何斌</v>
       </c>
     </row>
-    <row r="309" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="15" t="s">
         <v>2260</v>
       </c>
@@ -43078,7 +43084,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="15" t="s">
         <v>2264</v>
       </c>
@@ -43120,7 +43126,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="15" t="s">
         <v>2269</v>
       </c>
@@ -43162,7 +43168,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="312" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="15" t="s">
         <v>2271</v>
       </c>
@@ -43204,7 +43210,7 @@
         <v>宋必成</v>
       </c>
     </row>
-    <row r="313" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="18" t="s">
         <v>2273</v>
       </c>
@@ -43250,7 +43256,7 @@
         <v>王祥山 徐招莲</v>
       </c>
     </row>
-    <row r="314" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="18" t="s">
         <v>2273</v>
       </c>
@@ -43296,7 +43302,7 @@
         <v>刘文棹 谢美华</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="15" t="s">
         <v>2284</v>
       </c>
@@ -43338,7 +43344,7 @@
         <v>彭飞勇</v>
       </c>
     </row>
-    <row r="316" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="15" t="s">
         <v>2289</v>
       </c>
@@ -43382,7 +43388,7 @@
         <v>刘兰香 陈平云</v>
       </c>
     </row>
-    <row r="317" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="15" t="s">
         <v>2296</v>
       </c>
@@ -43418,7 +43424,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="15" t="s">
         <v>2297</v>
       </c>
@@ -43458,7 +43464,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="15" t="s">
         <v>2303</v>
       </c>
@@ -43506,7 +43512,7 @@
         <v>李为瑜 胡小青</v>
       </c>
     </row>
-    <row r="320" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="15" t="s">
         <v>2310</v>
       </c>
@@ -43554,7 +43560,7 @@
         <v>郭涛 胡嘉欣</v>
       </c>
     </row>
-    <row r="321" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="15" t="s">
         <v>2317</v>
       </c>
@@ -43592,7 +43598,7 @@
         <v/>
       </c>
     </row>
-    <row r="322" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="15" t="s">
         <v>2321</v>
       </c>
@@ -43632,7 +43638,7 @@
         <v/>
       </c>
     </row>
-    <row r="323" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="15" t="s">
         <v>2327</v>
       </c>
@@ -43668,7 +43674,7 @@
         <v/>
       </c>
     </row>
-    <row r="324" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="15" t="s">
         <v>2331</v>
       </c>
@@ -43708,7 +43714,7 @@
         <v/>
       </c>
     </row>
-    <row r="325" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="15" t="s">
         <v>2337</v>
       </c>
@@ -43746,7 +43752,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="15" t="s">
         <v>2342</v>
       </c>
@@ -43786,7 +43792,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="15" t="s">
         <v>2348</v>
       </c>
@@ -43826,7 +43832,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="15" t="s">
         <v>2354</v>
       </c>
@@ -43866,7 +43872,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="15" t="s">
         <v>2360</v>
       </c>
@@ -43906,7 +43912,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="15" t="s">
         <v>2366</v>
       </c>
@@ -43942,7 +43948,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="15" t="s">
         <v>2370</v>
       </c>
@@ -43986,7 +43992,7 @@
         <v>李兵 胡迎龙</v>
       </c>
     </row>
-    <row r="332" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="15" t="s">
         <v>2377</v>
       </c>
@@ -44032,7 +44038,7 @@
         <v>罗小峰 刘莉</v>
       </c>
     </row>
-    <row r="333" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="15" t="s">
         <v>2384</v>
       </c>
@@ -44078,7 +44084,7 @@
         <v>罗卫庆 罗美美</v>
       </c>
     </row>
-    <row r="334" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="15" t="s">
         <v>2391</v>
       </c>
@@ -44114,7 +44120,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="15" t="s">
         <v>2395</v>
       </c>
@@ -44150,7 +44156,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="15" t="s">
         <v>2399</v>
       </c>
@@ -44186,7 +44192,7 @@
         <v/>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="15" t="s">
         <v>2403</v>
       </c>
@@ -44226,7 +44232,7 @@
         <v/>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="15" t="s">
         <v>2409</v>
       </c>
@@ -44268,7 +44274,7 @@
         <v/>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="15" t="s">
         <v>2415</v>
       </c>
@@ -44308,7 +44314,7 @@
         <v/>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="15" t="s">
         <v>2416</v>
       </c>
@@ -44348,7 +44354,7 @@
         <v/>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="15" t="s">
         <v>2422</v>
       </c>
@@ -44388,7 +44394,7 @@
         <v/>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="15" t="s">
         <v>2423</v>
       </c>
@@ -44424,7 +44430,7 @@
         <v/>
       </c>
     </row>
-    <row r="343" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="15" t="s">
         <v>2427</v>
       </c>
@@ -44464,7 +44470,7 @@
         <v/>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="15" t="s">
         <v>2433</v>
       </c>
@@ -44508,7 +44514,7 @@
         <v>吕晨晨 魏磊</v>
       </c>
     </row>
-    <row r="345" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="15" t="s">
         <v>2440</v>
       </c>
@@ -44550,7 +44556,7 @@
         <v>曹声国</v>
       </c>
     </row>
-    <row r="346" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="15" t="s">
         <v>2445</v>
       </c>
@@ -44596,7 +44602,7 @@
         <v>段羊苟 罗玉兰</v>
       </c>
     </row>
-    <row r="347" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="6" t="s">
         <v>2448</v>
       </c>
@@ -44638,7 +44644,7 @@
         <v>戴鹏</v>
       </c>
     </row>
-    <row r="348" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="15" t="s">
         <v>2450</v>
       </c>
@@ -44680,7 +44686,7 @@
         <v>张经纶</v>
       </c>
     </row>
-    <row r="349" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="15" t="s">
         <v>2455</v>
       </c>
@@ -44722,7 +44728,7 @@
         <v>胡文龙</v>
       </c>
     </row>
-    <row r="350" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="15" t="s">
         <v>2460</v>
       </c>
@@ -44764,7 +44770,7 @@
         <v>彭逃华</v>
       </c>
     </row>
-    <row r="351" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="15" t="s">
         <v>2465</v>
       </c>
@@ -44812,7 +44818,7 @@
         <v>刘佳 宋勇晖</v>
       </c>
     </row>
-    <row r="352" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="15" t="s">
         <v>2472</v>
       </c>
@@ -44860,7 +44866,7 @@
         <v>刘军平 郭小梅</v>
       </c>
     </row>
-    <row r="353" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="15" t="s">
         <v>2479</v>
       </c>
@@ -44902,7 +44908,7 @@
         <v>吴弘</v>
       </c>
     </row>
-    <row r="354" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="15" t="s">
         <v>2484</v>
       </c>
@@ -44950,7 +44956,7 @@
         <v>郭惠钧 刘婷婷</v>
       </c>
     </row>
-    <row r="355" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="15" t="s">
         <v>2491</v>
       </c>
@@ -44998,7 +45004,7 @@
         <v>曾德志 朱淑芳</v>
       </c>
     </row>
-    <row r="356" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="15" t="s">
         <v>2498</v>
       </c>
@@ -45040,7 +45046,7 @@
         <v/>
       </c>
     </row>
-    <row r="357" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="15" t="s">
         <v>2504</v>
       </c>
@@ -45086,7 +45092,7 @@
         <v>卢忠星 吴丹</v>
       </c>
     </row>
-    <row r="358" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="15" t="s">
         <v>2511</v>
       </c>
@@ -45124,7 +45130,7 @@
         <v/>
       </c>
     </row>
-    <row r="359" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="15" t="s">
         <v>2517</v>
       </c>
@@ -45172,7 +45178,7 @@
         <v>曾小卿 袁维娟</v>
       </c>
     </row>
-    <row r="360" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="15" t="s">
         <v>2524</v>
       </c>
@@ -45208,7 +45214,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="15" t="s">
         <v>2528</v>
       </c>
@@ -45244,7 +45250,7 @@
         <v/>
       </c>
     </row>
-    <row r="362" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="15" t="s">
         <v>2532</v>
       </c>
@@ -45280,7 +45286,7 @@
         <v/>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="15" t="s">
         <v>2536</v>
       </c>
@@ -45320,7 +45326,7 @@
         <v/>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="15" t="s">
         <v>2542</v>
       </c>
@@ -45360,7 +45366,7 @@
         <v/>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="15" t="s">
         <v>2548</v>
       </c>
@@ -45520,7 +45526,7 @@
         <v>郭文</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="15" t="s">
         <v>2569</v>
       </c>
@@ -45560,7 +45566,7 @@
         <v>徐建国</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="15" t="s">
         <v>2574</v>
       </c>
@@ -45604,7 +45610,7 @@
         <v>李衡 李蓉</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="15" t="s">
         <v>2581</v>
       </c>
@@ -45692,7 +45698,7 @@
         <v>张艳 徐礼文</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="15" t="s">
         <v>2595</v>
       </c>
@@ -45734,7 +45740,7 @@
         <v>彭杰</v>
       </c>
     </row>
-    <row r="374" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="15" t="s">
         <v>2600</v>
       </c>
@@ -45770,7 +45776,7 @@
         <v/>
       </c>
     </row>
-    <row r="375" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="15" t="s">
         <v>2604</v>
       </c>
@@ -45818,7 +45824,7 @@
         <v>张硕 彭韶琴</v>
       </c>
     </row>
-    <row r="376" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="15" t="s">
         <v>2611</v>
       </c>
@@ -45866,7 +45872,7 @@
         <v>钟春光 肖春华</v>
       </c>
     </row>
-    <row r="377" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="15" t="s">
         <v>2618</v>
       </c>
@@ -45912,7 +45918,7 @@
         <v>刘先代 刘丽琴</v>
       </c>
     </row>
-    <row r="378" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="15" t="s">
         <v>2621</v>
       </c>
@@ -45958,7 +45964,7 @@
         <v>刘先代 刘丽琴</v>
       </c>
     </row>
-    <row r="379" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="15" t="s">
         <v>2623</v>
       </c>
@@ -45998,7 +46004,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="15" t="s">
         <v>2630</v>
       </c>
@@ -46034,7 +46040,7 @@
         <v/>
       </c>
     </row>
-    <row r="381" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="15" t="s">
         <v>2634</v>
       </c>
@@ -46074,7 +46080,7 @@
         <v/>
       </c>
     </row>
-    <row r="382" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="15" t="s">
         <v>2641</v>
       </c>
@@ -46120,7 +46126,7 @@
         <v>马玉娇 江海</v>
       </c>
     </row>
-    <row r="383" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="15" t="s">
         <v>2644</v>
       </c>
@@ -46166,7 +46172,7 @@
         <v>王婷 廖智茂</v>
       </c>
     </row>
-    <row r="384" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="15" t="s">
         <v>2651</v>
       </c>
@@ -46212,7 +46218,7 @@
         <v>王婷 廖智茂</v>
       </c>
     </row>
-    <row r="385" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="15" t="s">
         <v>2653</v>
       </c>
@@ -46254,7 +46260,7 @@
         <v>王清云</v>
       </c>
     </row>
-    <row r="386" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="15" t="s">
         <v>2659</v>
       </c>
@@ -46302,7 +46308,7 @@
         <v>高林 刘敏</v>
       </c>
     </row>
-    <row r="387" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="15" t="s">
         <v>2668</v>
       </c>
@@ -46344,7 +46350,7 @@
         <v>郭臧怡</v>
       </c>
     </row>
-    <row r="388" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="15" t="s">
         <v>2674</v>
       </c>
@@ -46392,7 +46398,7 @@
         <v>曾安琪 孙天黎</v>
       </c>
     </row>
-    <row r="389" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="15" t="s">
         <v>2683</v>
       </c>
@@ -46432,7 +46438,7 @@
         <v/>
       </c>
     </row>
-    <row r="390" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="15" t="s">
         <v>2690</v>
       </c>
@@ -46472,7 +46478,7 @@
         <v/>
       </c>
     </row>
-    <row r="391" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="15" t="s">
         <v>2697</v>
       </c>
@@ -46512,7 +46518,7 @@
         <v/>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="15" t="s">
         <v>2703</v>
       </c>
@@ -46560,7 +46566,7 @@
         <v>刘智龙 胡佳</v>
       </c>
     </row>
-    <row r="393" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="15" t="s">
         <v>2713</v>
       </c>
@@ -46606,7 +46612,7 @@
         <v>李仁华 吴小琴</v>
       </c>
     </row>
-    <row r="394" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="15" t="s">
         <v>2721</v>
       </c>
@@ -46654,7 +46660,7 @@
         <v>彭新风 刘辉</v>
       </c>
     </row>
-    <row r="395" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="15" t="s">
         <v>2724</v>
       </c>
@@ -46696,7 +46702,7 @@
         <v>谢吉翔</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="15" t="s">
         <v>2730</v>
       </c>
@@ -46738,7 +46744,7 @@
         <v>周水元</v>
       </c>
     </row>
-    <row r="397" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="15" t="s">
         <v>2736</v>
       </c>
@@ -46780,7 +46786,7 @@
         <v>冷小婷</v>
       </c>
     </row>
-    <row r="398" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="15" t="s">
         <v>2742</v>
       </c>
@@ -46822,7 +46828,7 @@
         <v>李梅英</v>
       </c>
     </row>
-    <row r="399" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="15" t="s">
         <v>2748</v>
       </c>
@@ -46868,7 +46874,7 @@
         <v>罗招凤 刘涛</v>
       </c>
     </row>
-    <row r="400" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="15" t="s">
         <v>2756</v>
       </c>
@@ -46904,7 +46910,7 @@
         <v/>
       </c>
     </row>
-    <row r="401" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="15" t="s">
         <v>2761</v>
       </c>
@@ -46944,7 +46950,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="15" t="s">
         <v>2768</v>
       </c>
@@ -46986,7 +46992,7 @@
         <v>李洪彬</v>
       </c>
     </row>
-    <row r="403" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="15" t="s">
         <v>2774</v>
       </c>
@@ -47034,7 +47040,7 @@
         <v>杨陈朱 黄强</v>
       </c>
     </row>
-    <row r="404" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="15" t="s">
         <v>2783</v>
       </c>
@@ -47076,7 +47082,7 @@
         <v>邹兰青</v>
       </c>
     </row>
-    <row r="405" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="15" t="s">
         <v>2785</v>
       </c>
@@ -47118,7 +47124,7 @@
         <v>刘金龙</v>
       </c>
     </row>
-    <row r="406" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="15" t="s">
         <v>2791</v>
       </c>
@@ -47164,7 +47170,7 @@
         <v>张欣 张丽花</v>
       </c>
     </row>
-    <row r="407" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="15" t="s">
         <v>2799</v>
       </c>
@@ -47212,7 +47218,7 @@
         <v>刘天学 罗芳</v>
       </c>
     </row>
-    <row r="408" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="15" t="s">
         <v>2808</v>
       </c>
@@ -47260,7 +47266,7 @@
         <v>罗英英 曾国慧</v>
       </c>
     </row>
-    <row r="409" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="15" t="s">
         <v>2817</v>
       </c>
@@ -47300,7 +47306,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="15" t="s">
         <v>2824</v>
       </c>
@@ -47340,7 +47346,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="15" t="s">
         <v>2831</v>
       </c>
@@ -47380,7 +47386,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="15" t="s">
         <v>2838</v>
       </c>
@@ -47416,7 +47422,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="15" t="s">
         <v>2843</v>
       </c>
@@ -47464,7 +47470,7 @@
         <v>许晓丽 郭力勇</v>
       </c>
     </row>
-    <row r="414" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="15" t="s">
         <v>2848</v>
       </c>
@@ -47512,7 +47518,7 @@
         <v>许晓丽 郭力勇</v>
       </c>
     </row>
-    <row r="415" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="15" t="s">
         <v>2850</v>
       </c>
@@ -47554,7 +47560,7 @@
         <v>钟婷</v>
       </c>
     </row>
-    <row r="416" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="15" t="s">
         <v>2856</v>
       </c>
@@ -47596,7 +47602,7 @@
         <v>黄扬</v>
       </c>
     </row>
-    <row r="417" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="15" t="s">
         <v>2862</v>
       </c>
@@ -47644,7 +47650,7 @@
         <v>周玥 周俊浩</v>
       </c>
     </row>
-    <row r="418" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="15" t="s">
         <v>2871</v>
       </c>
@@ -47684,7 +47690,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="15" t="s">
         <v>2878</v>
       </c>
@@ -47724,7 +47730,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="15" t="s">
         <v>2885</v>
       </c>
@@ -47764,7 +47770,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="15" t="s">
         <v>2892</v>
       </c>
@@ -47804,7 +47810,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="15" t="s">
         <v>2899</v>
       </c>
@@ -47852,7 +47858,7 @@
         <v>刘智新 汪爱华</v>
       </c>
     </row>
-    <row r="423" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="15" t="s">
         <v>2903</v>
       </c>
@@ -47892,7 +47898,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="15" t="s">
         <v>2910</v>
       </c>
@@ -47938,7 +47944,7 @@
         <v>黄学考 林仙燕</v>
       </c>
     </row>
-    <row r="425" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="15" t="s">
         <v>2913</v>
       </c>
@@ -47984,7 +47990,7 @@
         <v>黄学考 林仙燕</v>
       </c>
     </row>
-    <row r="426" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="15" t="s">
         <v>2915</v>
       </c>
@@ -48030,7 +48036,7 @@
         <v>吴宫兰 龙小卫</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="15" t="s">
         <v>2923</v>
       </c>
@@ -48072,7 +48078,7 @@
         <v>吴倩倩</v>
       </c>
     </row>
-    <row r="428" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="15" t="s">
         <v>2929</v>
       </c>
@@ -48114,7 +48120,7 @@
         <v>胡慧婷</v>
       </c>
     </row>
-    <row r="429" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="15" t="s">
         <v>2935</v>
       </c>
@@ -48154,7 +48160,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="15" t="s">
         <v>2942</v>
       </c>
@@ -48196,7 +48202,7 @@
         <v>周忠民</v>
       </c>
     </row>
-    <row r="431" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="15" t="s">
         <v>2948</v>
       </c>
@@ -48244,7 +48250,7 @@
         <v>郭朝东 邱峻</v>
       </c>
     </row>
-    <row r="432" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="15" t="s">
         <v>2957</v>
       </c>
@@ -48290,7 +48296,7 @@
         <v>喻智勇 梁珍兰</v>
       </c>
     </row>
-    <row r="433" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="15" t="s">
         <v>2959</v>
       </c>
@@ -48330,7 +48336,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="15" t="s">
         <v>2965</v>
       </c>
@@ -48370,7 +48376,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="15" t="s">
         <v>2972</v>
       </c>
@@ -48412,7 +48418,7 @@
         <v>刘华清</v>
       </c>
     </row>
-    <row r="436" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="15" t="s">
         <v>2978</v>
       </c>
@@ -48454,7 +48460,7 @@
         <v>刘华清</v>
       </c>
     </row>
-    <row r="437" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="15" t="s">
         <v>2980</v>
       </c>
@@ -48494,7 +48500,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="15" t="s">
         <v>2987</v>
       </c>
@@ -48534,7 +48540,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="15" t="s">
         <v>2994</v>
       </c>
@@ -48570,7 +48576,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="15" t="s">
         <v>2995</v>
       </c>
@@ -48610,7 +48616,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="15" t="s">
         <v>3002</v>
       </c>
@@ -48652,7 +48658,7 @@
         <v>王辉华</v>
       </c>
     </row>
-    <row r="442" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="15" t="s">
         <v>3008</v>
       </c>
@@ -48694,7 +48700,7 @@
         <v>朱小花</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="15" t="s">
         <v>3014</v>
       </c>
@@ -48742,7 +48748,7 @@
         <v>王海龙 施丹丹</v>
       </c>
     </row>
-    <row r="444" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="15" t="s">
         <v>3023</v>
       </c>
@@ -48784,7 +48790,7 @@
         <v>丁琴英</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="15" t="s">
         <v>3029</v>
       </c>
@@ -48826,7 +48832,7 @@
         <v>丁琴英</v>
       </c>
     </row>
-    <row r="446" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="15" t="s">
         <v>3031</v>
       </c>
@@ -48860,7 +48866,7 @@
         <v/>
       </c>
     </row>
-    <row r="447" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="15" t="s">
         <v>3033</v>
       </c>
@@ -48900,7 +48906,7 @@
         <v/>
       </c>
     </row>
-    <row r="448" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="15" t="s">
         <v>3040</v>
       </c>
@@ -48942,7 +48948,7 @@
         <v>罗敬财</v>
       </c>
     </row>
-    <row r="449" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="15" t="s">
         <v>3046</v>
       </c>
@@ -48978,7 +48984,7 @@
         <v/>
       </c>
     </row>
-    <row r="450" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="15" t="s">
         <v>3051</v>
       </c>
@@ -49018,7 +49024,7 @@
         <v/>
       </c>
     </row>
-    <row r="451" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="15" t="s">
         <v>3058</v>
       </c>
@@ -49060,7 +49066,7 @@
         <v>殷梅林</v>
       </c>
     </row>
-    <row r="452" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="15" t="s">
         <v>3064</v>
       </c>
@@ -49102,7 +49108,7 @@
         <v>肖静文</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="15" t="s">
         <v>3070</v>
       </c>
@@ -49144,7 +49150,7 @@
         <v>张呈香</v>
       </c>
     </row>
-    <row r="454" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="15" t="s">
         <v>3076</v>
       </c>
@@ -49186,7 +49192,7 @@
         <v>王志民</v>
       </c>
     </row>
-    <row r="455" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="15" t="s">
         <v>3082</v>
       </c>
@@ -49220,7 +49226,7 @@
         <v/>
       </c>
     </row>
-    <row r="456" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="15" t="s">
         <v>3086</v>
       </c>
@@ -49256,7 +49262,7 @@
         <v/>
       </c>
     </row>
-    <row r="457" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="15" t="s">
         <v>3091</v>
       </c>
@@ -49294,7 +49300,7 @@
         <v/>
       </c>
     </row>
-    <row r="458" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="15" t="s">
         <v>3097</v>
       </c>
@@ -49330,7 +49336,7 @@
         <v/>
       </c>
     </row>
-    <row r="459" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="15" t="s">
         <v>3102</v>
       </c>
@@ -49368,7 +49374,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="15" t="s">
         <v>3108</v>
       </c>
@@ -49404,7 +49410,7 @@
         <v/>
       </c>
     </row>
-    <row r="461" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="15" t="s">
         <v>3113</v>
       </c>
@@ -49444,7 +49450,7 @@
         <v/>
       </c>
     </row>
-    <row r="462" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="15" t="s">
         <v>3116</v>
       </c>
@@ -49482,7 +49488,7 @@
         <v/>
       </c>
     </row>
-    <row r="463" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="15" t="s">
         <v>3122</v>
       </c>
@@ -49520,7 +49526,7 @@
         <v/>
       </c>
     </row>
-    <row r="464" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="15" t="s">
         <v>3128</v>
       </c>
@@ -49558,7 +49564,7 @@
         <v/>
       </c>
     </row>
-    <row r="465" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="15" t="s">
         <v>3134</v>
       </c>
@@ -49602,7 +49608,7 @@
         <v/>
       </c>
     </row>
-    <row r="466" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="15" t="s">
         <v>3135</v>
       </c>
@@ -49636,7 +49642,7 @@
         <v/>
       </c>
     </row>
-    <row r="467" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="15" t="s">
         <v>3139</v>
       </c>
@@ -49678,7 +49684,7 @@
         <v>彭重扬</v>
       </c>
     </row>
-    <row r="468" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="15" t="s">
         <v>3145</v>
       </c>
@@ -49712,7 +49718,7 @@
         <v/>
       </c>
     </row>
-    <row r="469" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="15" t="s">
         <v>3146</v>
       </c>
@@ -49754,7 +49760,7 @@
         <v>邓盼</v>
       </c>
     </row>
-    <row r="470" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="15" t="s">
         <v>3152</v>
       </c>
@@ -49796,7 +49802,7 @@
         <v>钟青兰</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="15" t="s">
         <v>3158</v>
       </c>
@@ -49842,7 +49848,7 @@
         <v>王喜民 王小燕</v>
       </c>
     </row>
-    <row r="472" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="15" t="s">
         <v>3161</v>
       </c>
@@ -49888,7 +49894,7 @@
         <v>李伍毛 邹红英</v>
       </c>
     </row>
-    <row r="473" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="473" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="15" t="s">
         <v>3169</v>
       </c>
@@ -49928,7 +49934,7 @@
         <v/>
       </c>
     </row>
-    <row r="474" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="15" t="s">
         <v>3176</v>
       </c>
@@ -49966,7 +49972,7 @@
         <v/>
       </c>
     </row>
-    <row r="475" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="15" t="s">
         <v>3182</v>
       </c>
@@ -50004,7 +50010,7 @@
         <v/>
       </c>
     </row>
-    <row r="476" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="15" t="s">
         <v>3188</v>
       </c>
@@ -50044,7 +50050,7 @@
         <v/>
       </c>
     </row>
-    <row r="477" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="15" t="s">
         <v>3195</v>
       </c>
@@ -50084,7 +50090,7 @@
         <v/>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="15" t="s">
         <v>3202</v>
       </c>
@@ -50124,7 +50130,7 @@
         <v/>
       </c>
     </row>
-    <row r="479" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="15" t="s">
         <v>3209</v>
       </c>
@@ -50164,7 +50170,7 @@
         <v/>
       </c>
     </row>
-    <row r="480" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="15" t="s">
         <v>3216</v>
       </c>
@@ -50202,7 +50208,7 @@
         <v/>
       </c>
     </row>
-    <row r="481" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="15" t="s">
         <v>3222</v>
       </c>
@@ -50244,7 +50250,7 @@
         <v>盛德豪</v>
       </c>
     </row>
-    <row r="482" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482" s="15" t="s">
         <v>3228</v>
       </c>
@@ -50286,7 +50292,7 @@
         <v>盛德豪</v>
       </c>
     </row>
-    <row r="483" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483" s="15" t="s">
         <v>3230</v>
       </c>
@@ -50332,7 +50338,7 @@
         <v>邓高生 严小英</v>
       </c>
     </row>
-    <row r="484" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484" s="15" t="s">
         <v>3238</v>
       </c>
@@ -50380,7 +50386,7 @@
         <v>宋光太 匡秀华</v>
       </c>
     </row>
-    <row r="485" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485" s="15" t="s">
         <v>3247</v>
       </c>
@@ -50426,7 +50432,7 @@
         <v>杨晓锐 黄建华</v>
       </c>
     </row>
-    <row r="486" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486" s="15" t="s">
         <v>3255</v>
       </c>
@@ -50468,7 +50474,7 @@
         <v>宋文佳</v>
       </c>
     </row>
-    <row r="487" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487" s="15" t="s">
         <v>3261</v>
       </c>
@@ -50508,7 +50514,7 @@
         <v/>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488" s="15" t="s">
         <v>3268</v>
       </c>
@@ -50550,7 +50556,7 @@
         <v>李树光</v>
       </c>
     </row>
-    <row r="489" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="489" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489" s="15" t="s">
         <v>3272</v>
       </c>
@@ -50596,7 +50602,7 @@
         <v>毛年香 王明强</v>
       </c>
     </row>
-    <row r="490" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="490" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490" s="15" t="s">
         <v>3275</v>
       </c>
@@ -50636,7 +50642,7 @@
         <v/>
       </c>
     </row>
-    <row r="491" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="491" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491" s="15" t="s">
         <v>3282</v>
       </c>
@@ -50676,7 +50682,7 @@
         <v/>
       </c>
     </row>
-    <row r="492" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="492" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492" s="15" t="s">
         <v>3289</v>
       </c>
@@ -50714,7 +50720,7 @@
         <v/>
       </c>
     </row>
-    <row r="493" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="493" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493" s="15" t="s">
         <v>3295</v>
       </c>
@@ -50754,7 +50760,7 @@
         <v/>
       </c>
     </row>
-    <row r="494" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="494" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A494" s="15" t="s">
         <v>3302</v>
       </c>
@@ -50790,7 +50796,7 @@
         <v/>
       </c>
     </row>
-    <row r="495" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="495" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A495" s="15" t="s">
         <v>3307</v>
       </c>
@@ -50830,7 +50836,7 @@
         <v/>
       </c>
     </row>
-    <row r="496" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="496" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A496" s="15" t="s">
         <v>3314</v>
       </c>
@@ -50872,7 +50878,7 @@
         <v/>
       </c>
     </row>
-    <row r="497" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="497" spans="1:15" ht="24" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497" s="15" t="s">
         <v>3321</v>
       </c>
@@ -50909,7 +50915,7 @@
         <v/>
       </c>
     </row>
-    <row r="498" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="498" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A498" s="15" t="s">
         <v>3327</v>
       </c>
@@ -50949,7 +50955,7 @@
         <v/>
       </c>
     </row>
-    <row r="499" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="499" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A499" s="15" t="s">
         <v>3334</v>
       </c>
@@ -50985,7 +50991,7 @@
         <v/>
       </c>
     </row>
-    <row r="500" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="500" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A500" s="15" t="s">
         <v>3339</v>
       </c>
@@ -51025,7 +51031,7 @@
         <v/>
       </c>
     </row>
-    <row r="501" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="501" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A501" s="15" t="s">
         <v>3346</v>
       </c>
@@ -51061,7 +51067,7 @@
         <v/>
       </c>
     </row>
-    <row r="502" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="502" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A502" s="15" t="s">
         <v>3351</v>
       </c>
@@ -51101,7 +51107,7 @@
         <v/>
       </c>
     </row>
-    <row r="503" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="503" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A503" s="15" t="s">
         <v>3358</v>
       </c>
@@ -51143,7 +51149,7 @@
         <v>王小慧</v>
       </c>
     </row>
-    <row r="504" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="504" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A504" s="15" t="s">
         <v>3364</v>
       </c>
@@ -51235,7 +51241,7 @@
         <v>刘镇平 彭满娇</v>
       </c>
     </row>
-    <row r="506" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="506" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A506" s="15" t="s">
         <v>3374</v>
       </c>
@@ -51279,7 +51285,7 @@
         <v>戴林军 陈素贞</v>
       </c>
     </row>
-    <row r="507" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="507" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A507" s="15" t="s">
         <v>3382</v>
       </c>
@@ -51319,7 +51325,7 @@
         <v>李锋明</v>
       </c>
     </row>
-    <row r="508" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="508" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A508" s="15" t="s">
         <v>3388</v>
       </c>
@@ -51361,7 +51367,7 @@
         <v>文雯</v>
       </c>
     </row>
-    <row r="509" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="509" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A509" s="15" t="s">
         <v>3394</v>
       </c>
@@ -51403,7 +51409,7 @@
         <v>朱雪莲</v>
       </c>
     </row>
-    <row r="510" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="510" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A510" s="15" t="s">
         <v>3400</v>
       </c>
@@ -51449,7 +51455,7 @@
         <v>张细苟 谭春莲</v>
       </c>
     </row>
-    <row r="511" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="511" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A511" s="15" t="s">
         <v>3408</v>
       </c>
@@ -51497,7 +51503,7 @@
         <v>郭芳金 卢芳兰</v>
       </c>
     </row>
-    <row r="512" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="512" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A512" s="15" t="s">
         <v>3417</v>
       </c>
@@ -51537,7 +51543,7 @@
         <v/>
       </c>
     </row>
-    <row r="513" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="513" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A513" s="15" t="s">
         <v>3424</v>
       </c>
@@ -51577,7 +51583,7 @@
         <v/>
       </c>
     </row>
-    <row r="514" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="514" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A514" s="15" t="s">
         <v>3431</v>
       </c>
@@ -51617,7 +51623,7 @@
         <v/>
       </c>
     </row>
-    <row r="515" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="515" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A515" s="15" t="s">
         <v>3438</v>
       </c>
@@ -51653,7 +51659,7 @@
         <v/>
       </c>
     </row>
-    <row r="516" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="516" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A516" s="15" t="s">
         <v>3443</v>
       </c>
@@ -51689,7 +51695,7 @@
         <v/>
       </c>
     </row>
-    <row r="517" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="517" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A517" s="15" t="s">
         <v>3448</v>
       </c>
@@ -51729,7 +51735,7 @@
         <v/>
       </c>
     </row>
-    <row r="518" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="518" spans="1:15" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518" s="15" t="s">
         <v>3455</v>
       </c>
@@ -51765,7 +51771,7 @@
         <v/>
       </c>
     </row>
-    <row r="519" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="519" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A519" s="15" t="s">
         <v>3460</v>
       </c>
@@ -51813,7 +51819,7 @@
         <v>宋文斌 肖丽</v>
       </c>
     </row>
-    <row r="520" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="520" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A520" s="15" t="s">
         <v>3469</v>
       </c>
@@ -51855,7 +51861,7 @@
         <v>郭贞云</v>
       </c>
     </row>
-    <row r="521" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="521" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A521" s="15" t="s">
         <v>3475</v>
       </c>
@@ -51903,7 +51909,7 @@
         <v>李娟 胡昊</v>
       </c>
     </row>
-    <row r="522" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="522" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A522" s="15" t="s">
         <v>3484</v>
       </c>
@@ -51949,7 +51955,7 @@
         <v>李娜 肖诗靓</v>
       </c>
     </row>
-    <row r="523" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="523" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A523" s="15" t="s">
         <v>3492</v>
       </c>
@@ -51997,7 +52003,7 @@
         <v>周学勤 邓俊超</v>
       </c>
     </row>
-    <row r="524" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="524" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A524" s="15" t="s">
         <v>3501</v>
       </c>
@@ -52033,7 +52039,7 @@
         <v/>
       </c>
     </row>
-    <row r="525" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="525" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A525" s="15" t="s">
         <v>3506</v>
       </c>
@@ -52075,7 +52081,7 @@
         <v/>
       </c>
     </row>
-    <row r="526" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="526" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A526" s="15" t="s">
         <v>3514</v>
       </c>
@@ -52121,7 +52127,7 @@
         <v>黄钟龙 李娟红</v>
       </c>
     </row>
-    <row r="527" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="527" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527" s="15" t="s">
         <v>3522</v>
       </c>
@@ -52169,7 +52175,7 @@
         <v>田鹏显 雷莲芳</v>
       </c>
     </row>
-    <row r="528" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="528" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528" s="15" t="s">
         <v>3531</v>
       </c>
@@ -52217,7 +52223,7 @@
         <v>廖声兵 谢金香</v>
       </c>
     </row>
-    <row r="529" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="529" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529" s="15" t="s">
         <v>3540</v>
       </c>
@@ -52259,7 +52265,7 @@
         <v>杨成浪</v>
       </c>
     </row>
-    <row r="530" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="530" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530" s="15" t="s">
         <v>3546</v>
       </c>
@@ -52293,7 +52299,7 @@
         <v/>
       </c>
     </row>
-    <row r="531" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="531" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531" s="15" t="s">
         <v>3550</v>
       </c>
@@ -52327,7 +52333,7 @@
         <v/>
       </c>
     </row>
-    <row r="532" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="532" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532" s="15" t="s">
         <v>3554</v>
       </c>
@@ -52361,7 +52367,7 @@
         <v/>
       </c>
     </row>
-    <row r="533" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="533" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533" s="15" t="s">
         <v>3558</v>
       </c>
@@ -52399,7 +52405,7 @@
         <v/>
       </c>
     </row>
-    <row r="534" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="534" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534" s="15" t="s">
         <v>3564</v>
       </c>
@@ -52437,7 +52443,7 @@
         <v/>
       </c>
     </row>
-    <row r="535" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="535" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535" s="15" t="s">
         <v>3570</v>
       </c>
@@ -52475,7 +52481,7 @@
         <v/>
       </c>
     </row>
-    <row r="536" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="536" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536" s="15" t="s">
         <v>3576</v>
       </c>
@@ -52513,7 +52519,7 @@
         <v/>
       </c>
     </row>
-    <row r="537" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="537" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537" s="15" t="s">
         <v>3582</v>
       </c>
@@ -52551,7 +52557,7 @@
         <v/>
       </c>
     </row>
-    <row r="538" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="538" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538" s="15" t="s">
         <v>3588</v>
       </c>
@@ -52599,7 +52605,7 @@
         <v>肖文婧 吴德强</v>
       </c>
     </row>
-    <row r="539" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="539" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539" s="15" t="s">
         <v>3597</v>
       </c>
@@ -52647,7 +52653,7 @@
         <v>郭婷 曾纪帅</v>
       </c>
     </row>
-    <row r="540" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="540" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540" s="15" t="s">
         <v>3606</v>
       </c>
@@ -52695,7 +52701,7 @@
         <v>古桂兰 赖文祥</v>
       </c>
     </row>
-    <row r="541" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="541" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541" s="15" t="s">
         <v>3615</v>
       </c>
@@ -52741,7 +52747,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="542" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="542" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542" s="15" t="s">
         <v>3623</v>
       </c>
@@ -52777,7 +52783,7 @@
         <v/>
       </c>
     </row>
-    <row r="543" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="543" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543" s="15" t="s">
         <v>3628</v>
       </c>
@@ -52823,7 +52829,7 @@
         <v>高惠明 刘诗华</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="544" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A544" s="15" t="s">
         <v>3636</v>
       </c>
@@ -52871,7 +52877,7 @@
         <v>郭玉令 陈小燕</v>
       </c>
     </row>
-    <row r="545" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="545" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A545" s="15" t="s">
         <v>3645</v>
       </c>
@@ -52913,7 +52919,7 @@
         <v>吉安市永宾商贸有限公司</v>
       </c>
     </row>
-    <row r="546" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="546" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A546" s="15" t="s">
         <v>3651</v>
       </c>
@@ -52947,7 +52953,7 @@
         <v/>
       </c>
     </row>
-    <row r="547" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="547" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A547" s="15" t="s">
         <v>3655</v>
       </c>
@@ -52985,7 +52991,7 @@
         <v/>
       </c>
     </row>
-    <row r="548" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="548" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A548" s="15" t="s">
         <v>3661</v>
       </c>
@@ -53023,7 +53029,7 @@
         <v/>
       </c>
     </row>
-    <row r="549" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="549" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A549" s="15" t="s">
         <v>3667</v>
       </c>
@@ -53059,7 +53065,7 @@
         <v/>
       </c>
     </row>
-    <row r="550" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="550" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A550" s="15" t="s">
         <v>3672</v>
       </c>
@@ -53097,7 +53103,7 @@
         <v/>
       </c>
     </row>
-    <row r="551" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="551" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A551" s="15" t="s">
         <v>3678</v>
       </c>
@@ -53131,7 +53137,7 @@
         <v/>
       </c>
     </row>
-    <row r="552" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="552" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A552" s="15" t="s">
         <v>3682</v>
       </c>
@@ -53165,7 +53171,7 @@
         <v/>
       </c>
     </row>
-    <row r="553" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="553" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A553" s="15" t="s">
         <v>3686</v>
       </c>
@@ -53203,7 +53209,7 @@
         <v/>
       </c>
     </row>
-    <row r="554" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="554" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A554" s="15" t="s">
         <v>3692</v>
       </c>
@@ -53245,7 +53251,7 @@
         <v>李珍红</v>
       </c>
     </row>
-    <row r="555" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="555" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A555" s="15" t="s">
         <v>3698</v>
       </c>
@@ -53293,7 +53299,7 @@
         <v>向敏 李荣</v>
       </c>
     </row>
-    <row r="556" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="556" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A556" s="15" t="s">
         <v>3707</v>
       </c>
@@ -53331,7 +53337,7 @@
         <v/>
       </c>
     </row>
-    <row r="557" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="557" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A557" s="15" t="s">
         <v>3713</v>
       </c>
@@ -53379,7 +53385,7 @@
         <v>肖桂兰 林善华</v>
       </c>
     </row>
-    <row r="558" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="558" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A558" s="15" t="s">
         <v>3722</v>
       </c>
@@ -53417,7 +53423,7 @@
         <v/>
       </c>
     </row>
-    <row r="559" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="559" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A559" s="15" t="s">
         <v>3728</v>
       </c>
@@ -53465,7 +53471,7 @@
         <v>王红艳 刘利</v>
       </c>
     </row>
-    <row r="560" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="560" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A560" s="15" t="s">
         <v>3737</v>
       </c>
@@ -53499,7 +53505,7 @@
         <v/>
       </c>
     </row>
-    <row r="561" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="561" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A561" s="15" t="s">
         <v>3741</v>
       </c>
@@ -53545,7 +53551,7 @@
         <v>黄少英 肖向阳</v>
       </c>
     </row>
-    <row r="562" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="562" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A562" s="15" t="s">
         <v>3744</v>
       </c>
@@ -53587,7 +53593,7 @@
         <v>周小燕</v>
       </c>
     </row>
-    <row r="563" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="563" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A563" s="15" t="s">
         <v>3750</v>
       </c>
@@ -53629,7 +53635,7 @@
         <v>陈军梅</v>
       </c>
     </row>
-    <row r="564" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="564" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A564" s="15" t="s">
         <v>3756</v>
       </c>
@@ -53677,7 +53683,7 @@
         <v>况根秀 张伟东</v>
       </c>
     </row>
-    <row r="565" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="565" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A565" s="15" t="s">
         <v>3765</v>
       </c>
@@ -53719,7 +53725,7 @@
         <v>张文娟</v>
       </c>
     </row>
-    <row r="566" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="566" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A566" s="15" t="s">
         <v>3768</v>
       </c>
@@ -53761,7 +53767,7 @@
         <v>庄宝娟</v>
       </c>
     </row>
-    <row r="567" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="567" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A567" s="15" t="s">
         <v>3774</v>
       </c>
@@ -53795,7 +53801,7 @@
         <v/>
       </c>
     </row>
-    <row r="568" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="568" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A568" s="15" t="s">
         <v>3778</v>
       </c>
@@ -53833,7 +53839,7 @@
         <v/>
       </c>
     </row>
-    <row r="569" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="569" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A569" s="15" t="s">
         <v>3784</v>
       </c>
@@ -53871,7 +53877,7 @@
         <v/>
       </c>
     </row>
-    <row r="570" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="570" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A570" s="15" t="s">
         <v>3790</v>
       </c>
@@ -53905,7 +53911,7 @@
         <v/>
       </c>
     </row>
-    <row r="571" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="571" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A571" s="15" t="s">
         <v>3794</v>
       </c>
@@ -53939,7 +53945,7 @@
         <v/>
       </c>
     </row>
-    <row r="572" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="572" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A572" s="15" t="s">
         <v>3798</v>
       </c>
@@ -53977,7 +53983,7 @@
         <v/>
       </c>
     </row>
-    <row r="573" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="573" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A573" s="15" t="s">
         <v>3804</v>
       </c>
@@ -54015,7 +54021,7 @@
         <v/>
       </c>
     </row>
-    <row r="574" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="574" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A574" s="15" t="s">
         <v>3810</v>
       </c>
@@ -54051,7 +54057,7 @@
         <v/>
       </c>
     </row>
-    <row r="575" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="575" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A575" s="15" t="s">
         <v>3815</v>
       </c>
@@ -54223,7 +54229,7 @@
         <v>刘启为</v>
       </c>
     </row>
-    <row r="579" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="579" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A579" s="15" t="s">
         <v>3829</v>
       </c>
@@ -54255,7 +54261,7 @@
         <v/>
       </c>
     </row>
-    <row r="580" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="580" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A580" s="15" t="s">
         <v>3832</v>
       </c>
@@ -54291,7 +54297,7 @@
         <v/>
       </c>
     </row>
-    <row r="581" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="581" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A581" s="15" t="s">
         <v>3837</v>
       </c>
@@ -54325,7 +54331,7 @@
         <v/>
       </c>
     </row>
-    <row r="582" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="582" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A582" s="15" t="s">
         <v>3841</v>
       </c>
@@ -54359,7 +54365,7 @@
         <v/>
       </c>
     </row>
-    <row r="583" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="583" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A583" s="15" t="s">
         <v>3845</v>
       </c>
@@ -54397,7 +54403,7 @@
         <v/>
       </c>
     </row>
-    <row r="584" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="584" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A584" s="15" t="s">
         <v>3851</v>
       </c>
@@ -54435,7 +54441,7 @@
         <v/>
       </c>
     </row>
-    <row r="585" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="585" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A585" s="15" t="s">
         <v>3857</v>
       </c>
@@ -54483,7 +54489,7 @@
         <v>刘韬 朱超</v>
       </c>
     </row>
-    <row r="586" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="586" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A586" s="15" t="s">
         <v>3866</v>
       </c>
@@ -54525,7 +54531,7 @@
         <v>邹龙滔</v>
       </c>
     </row>
-    <row r="587" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="587" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A587" s="15" t="s">
         <v>3872</v>
       </c>
@@ -54571,7 +54577,7 @@
         <v>叶师军 孙小琴</v>
       </c>
     </row>
-    <row r="588" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="588" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A588" s="15" t="s">
         <v>3880</v>
       </c>
@@ -54613,7 +54619,7 @@
         <v>黎舟</v>
       </c>
     </row>
-    <row r="589" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="589" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A589" s="15" t="s">
         <v>3886</v>
       </c>
@@ -54659,7 +54665,7 @@
         <v>周锡高 曾丽军</v>
       </c>
     </row>
-    <row r="590" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="590" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A590" s="15" t="s">
         <v>3894</v>
       </c>
@@ -54695,7 +54701,7 @@
         <v/>
       </c>
     </row>
-    <row r="591" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="591" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A591" s="15" t="s">
         <v>3898</v>
       </c>
@@ -54737,7 +54743,7 @@
         <v>柯建西</v>
       </c>
     </row>
-    <row r="592" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="592" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A592" s="15" t="s">
         <v>3904</v>
       </c>
@@ -54867,7 +54873,7 @@
         <v>罗明 宋丹丹</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="595" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A595" s="15" t="s">
         <v>3922</v>
       </c>
@@ -54915,7 +54921,7 @@
         <v>李建斌 刘小玲</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="596" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A596" s="15" t="s">
         <v>3931</v>
       </c>
@@ -55039,7 +55045,7 @@
         <v>陈明 罗飞飞</v>
       </c>
     </row>
-    <row r="599" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="599" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A599" s="15" t="s">
         <v>3950</v>
       </c>
@@ -55073,7 +55079,7 @@
         <v/>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="600" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A600" s="15" t="s">
         <v>3954</v>
       </c>
@@ -55111,7 +55117,7 @@
         <v/>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="601" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A601" s="15" t="s">
         <v>3960</v>
       </c>
@@ -55149,7 +55155,7 @@
         <v/>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="602" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A602" s="15" t="s">
         <v>3966</v>
       </c>
@@ -55197,7 +55203,7 @@
         <v>庞瑶瑶 邹韬</v>
       </c>
     </row>
-    <row r="603" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="603" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A603" s="15" t="s">
         <v>3975</v>
       </c>
@@ -55239,7 +55245,7 @@
         <v>邓钊</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="604" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A604" s="15" t="s">
         <v>3981</v>
       </c>
@@ -55277,7 +55283,7 @@
         <v/>
       </c>
     </row>
-    <row r="605" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="605" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A605" s="15" t="s">
         <v>3987</v>
       </c>
@@ -55323,7 +55329,7 @@
         <v>肖明华 贾巧英</v>
       </c>
     </row>
-    <row r="606" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="606" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A606" s="15" t="s">
         <v>3995</v>
       </c>
@@ -55365,7 +55371,7 @@
         <v>曾亮星</v>
       </c>
     </row>
-    <row r="607" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="607" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A607" s="15" t="s">
         <v>4001</v>
       </c>
@@ -55407,7 +55413,7 @@
         <v>宋国军</v>
       </c>
     </row>
-    <row r="608" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="608" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A608" s="15" t="s">
         <v>4007</v>
       </c>
@@ -55455,7 +55461,7 @@
         <v>邱美胜 刘美华</v>
       </c>
     </row>
-    <row r="609" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="609" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A609" s="15" t="s">
         <v>4016</v>
       </c>
@@ -55497,7 +55503,7 @@
         <v>曾群花</v>
       </c>
     </row>
-    <row r="610" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="610" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A610" s="15" t="s">
         <v>4022</v>
       </c>
@@ -55529,7 +55535,7 @@
         <v/>
       </c>
     </row>
-    <row r="611" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="611" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A611" s="15" t="s">
         <v>4025</v>
       </c>
@@ -55571,7 +55577,7 @@
         <v>赵慧平</v>
       </c>
     </row>
-    <row r="612" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="612" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A612" s="15" t="s">
         <v>4031</v>
       </c>
@@ -55605,7 +55611,7 @@
         <v/>
       </c>
     </row>
-    <row r="613" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="613" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A613" s="15" t="s">
         <v>4035</v>
       </c>
@@ -55643,7 +55649,7 @@
         <v/>
       </c>
     </row>
-    <row r="614" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="614" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A614" s="15" t="s">
         <v>4041</v>
       </c>
@@ -55681,7 +55687,7 @@
         <v/>
       </c>
     </row>
-    <row r="615" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="615" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A615" s="15" t="s">
         <v>4047</v>
       </c>
@@ -55727,7 +55733,7 @@
         <v>郭生姑 李志云</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="616" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A616" s="15" t="s">
         <v>4055</v>
       </c>
@@ -55761,7 +55767,7 @@
         <v/>
       </c>
     </row>
-    <row r="617" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="617" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A617" s="15" t="s">
         <v>4059</v>
       </c>
@@ -55809,7 +55815,7 @@
         <v>潘明圣 谢美艳</v>
       </c>
     </row>
-    <row r="618" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="618" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A618" s="15" t="s">
         <v>4068</v>
       </c>
@@ -55893,7 +55899,7 @@
         <v>胡悦 曾广鑫</v>
       </c>
     </row>
-    <row r="620" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="620" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A620" s="15" t="s">
         <v>4081</v>
       </c>
@@ -55935,7 +55941,7 @@
         <v>欧阳琼</v>
       </c>
     </row>
-    <row r="621" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="621" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A621" s="15" t="s">
         <v>4087</v>
       </c>
@@ -55977,7 +55983,7 @@
         <v>胡玥容</v>
       </c>
     </row>
-    <row r="622" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="622" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A622" s="15" t="s">
         <v>4093</v>
       </c>
@@ -56019,7 +56025,7 @@
         <v>郭乙航</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="623" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A623" s="15" t="s">
         <v>4099</v>
       </c>
@@ -56057,7 +56063,7 @@
         <v/>
       </c>
     </row>
-    <row r="624" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="624" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A624" s="15" t="s">
         <v>4105</v>
       </c>
@@ -56099,7 +56105,7 @@
         <v>王小雪</v>
       </c>
     </row>
-    <row r="625" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="625" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A625" s="15" t="s">
         <v>4111</v>
       </c>
@@ -56145,7 +56151,7 @@
         <v>吴细凤 胡财保</v>
       </c>
     </row>
-    <row r="626" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="626" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A626" s="15" t="s">
         <v>4119</v>
       </c>
@@ -56181,7 +56187,7 @@
         <v/>
       </c>
     </row>
-    <row r="627" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="627" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A627" s="15" t="s">
         <v>4120</v>
       </c>
@@ -56221,7 +56227,7 @@
         <v>张丽华</v>
       </c>
     </row>
-    <row r="628" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="628" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A628" s="15" t="s">
         <v>4126</v>
       </c>
@@ -56269,7 +56275,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="629" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="629" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A629" s="15" t="s">
         <v>4130</v>
       </c>
@@ -56317,7 +56323,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="630" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="630" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A630" s="15" t="s">
         <v>4132</v>
       </c>
@@ -56359,7 +56365,7 @@
         <v>吉安华通物流中心有限公司</v>
       </c>
     </row>
-    <row r="631" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="631" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A631" s="15" t="s">
         <v>4138</v>
       </c>
@@ -56401,7 +56407,7 @@
         <v>王兰萍</v>
       </c>
     </row>
-    <row r="632" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="632" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A632" s="15" t="s">
         <v>4144</v>
       </c>
@@ -56449,7 +56455,7 @@
         <v>孙明华 邓芳</v>
       </c>
     </row>
-    <row r="633" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="633" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A633" s="15" t="s">
         <v>4153</v>
       </c>
@@ -56485,7 +56491,7 @@
         <v/>
       </c>
     </row>
-    <row r="634" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="634" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A634" s="15" t="s">
         <v>4158</v>
       </c>
@@ -56519,7 +56525,7 @@
         <v/>
       </c>
     </row>
-    <row r="635" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="635" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A635" s="15" t="s">
         <v>4162</v>
       </c>
@@ -56553,7 +56559,7 @@
         <v/>
       </c>
     </row>
-    <row r="636" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="636" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A636" s="15" t="s">
         <v>4166</v>
       </c>
@@ -56601,7 +56607,7 @@
         <v>何小梅 李京忠</v>
       </c>
     </row>
-    <row r="637" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="637" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A637" s="15" t="s">
         <v>4175</v>
       </c>
@@ -56649,7 +56655,7 @@
         <v>邹建岭 麻丽斯</v>
       </c>
     </row>
-    <row r="638" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="638" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A638" s="15" t="s">
         <v>4184</v>
       </c>
@@ -56691,7 +56697,7 @@
         <v>彭杰</v>
       </c>
     </row>
-    <row r="639" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="639" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A639" s="15" t="s">
         <v>4188</v>
       </c>
@@ -56725,7 +56731,7 @@
         <v/>
       </c>
     </row>
-    <row r="640" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="640" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A640" s="15" t="s">
         <v>4192</v>
       </c>
@@ -56759,7 +56765,7 @@
         <v/>
       </c>
     </row>
-    <row r="641" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="641" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A641" s="15" t="s">
         <v>4196</v>
       </c>
@@ -56807,7 +56813,7 @@
         <v>肖智光 杨平</v>
       </c>
     </row>
-    <row r="642" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="642" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A642" s="15" t="s">
         <v>4205</v>
       </c>
@@ -56849,7 +56855,7 @@
         <v>胡丽凤</v>
       </c>
     </row>
-    <row r="643" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="643" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A643" s="15" t="s">
         <v>4211</v>
       </c>
@@ -56891,7 +56897,7 @@
         <v>杨恒熠</v>
       </c>
     </row>
-    <row r="644" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="644" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A644" s="15" t="s">
         <v>4217</v>
       </c>
@@ -56937,7 +56943,7 @@
         <v>刘美华 陈通元</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="645" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A645" s="15" t="s">
         <v>4224</v>
       </c>
@@ -56979,7 +56985,7 @@
         <v>梁秋茂</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="646" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A646" s="15" t="s">
         <v>4230</v>
       </c>
@@ -57027,7 +57033,7 @@
         <v>李军勇 王头女</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="647" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A647" s="15" t="s">
         <v>4239</v>
       </c>
@@ -57065,7 +57071,7 @@
         <v/>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="648" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A648" s="15" t="s">
         <v>4245</v>
       </c>
@@ -57099,7 +57105,7 @@
         <v/>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="649" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A649" s="15" t="s">
         <v>4249</v>
       </c>
@@ -57133,7 +57139,7 @@
         <v/>
       </c>
     </row>
-    <row r="650" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="650" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A650" s="15" t="s">
         <v>4253</v>
       </c>
@@ -57169,7 +57175,7 @@
         <v/>
       </c>
     </row>
-    <row r="651" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="651" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A651" s="15" t="s">
         <v>4258</v>
       </c>
@@ -57215,7 +57221,7 @@
         <v>郭洋 徐健</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="652" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A652" s="15" t="s">
         <v>4266</v>
       </c>
@@ -57261,7 +57267,7 @@
         <v>郭洋 徐健</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="653" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A653" s="15" t="s">
         <v>4268</v>
       </c>
@@ -57307,7 +57313,7 @@
         <v>郭君花 胡春凯</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="654" spans="1:15" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A654" s="15" t="s">
         <v>4276</v>
       </c>
@@ -57353,7 +57359,7 @@
         <v>郭君花 胡春凯</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="655" spans="1:15" ht="27.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A655" s="15" t="s">
         <v>4278</v>
       </c>
@@ -57399,7 +57405,7 @@
         <v>傅欢 刘家华</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="656" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A656" s="15" t="s">
         <v>4283</v>
       </c>
@@ -57441,7 +57447,7 @@
         <v>刘攀</v>
       </c>
     </row>
-    <row r="657" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="657" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A657" s="15" t="s">
         <v>4289</v>
       </c>
@@ -57483,7 +57489,7 @@
         <v>杨志星</v>
       </c>
     </row>
-    <row r="658" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="658" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A658" s="15" t="s">
         <v>4295</v>
       </c>
@@ -57531,7 +57537,7 @@
         <v>石朝军 肖美凤</v>
       </c>
     </row>
-    <row r="659" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="659" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A659" s="15" t="s">
         <v>4304</v>
       </c>
@@ -57577,7 +57583,7 @@
         <v>刘木法 梁茶花</v>
       </c>
     </row>
-    <row r="660" spans="1:15" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="660" spans="1:15" ht="29.1" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A660" s="15" t="s">
         <v>4312</v>
       </c>
@@ -57597,7 +57603,9 @@
         <v>4317</v>
       </c>
       <c r="G660" s="15"/>
-      <c r="H660" s="15"/>
+      <c r="H660" s="15" t="s">
+        <v>4310</v>
+      </c>
       <c r="I660" s="15"/>
       <c r="J660" s="6" t="s">
         <v>528</v>
@@ -57615,7 +57623,7 @@
         <v/>
       </c>
     </row>
-    <row r="661" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="661" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A661" s="15" t="s">
         <v>4318</v>
       </c>
@@ -57657,7 +57665,7 @@
         <v>陈嘉怡</v>
       </c>
     </row>
-    <row r="662" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="662" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A662" s="15" t="s">
         <v>4324</v>
       </c>
@@ -57705,7 +57713,7 @@
         <v>兰成 李楠</v>
       </c>
     </row>
-    <row r="663" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="663" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A663" s="15" t="s">
         <v>4333</v>
       </c>
@@ -57753,7 +57761,7 @@
         <v>傅维成 段旭慧</v>
       </c>
     </row>
-    <row r="664" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="664" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A664" s="15" t="s">
         <v>4342</v>
       </c>
@@ -57795,7 +57803,7 @@
         <v>邓连珠</v>
       </c>
     </row>
-    <row r="665" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="665" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A665" s="15" t="s">
         <v>4348</v>
       </c>
@@ -57841,7 +57849,7 @@
         <v>罗梨 李显海</v>
       </c>
     </row>
-    <row r="666" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="666" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A666" s="15" t="s">
         <v>4356</v>
       </c>
@@ -57883,7 +57891,7 @@
         <v>刘毓</v>
       </c>
     </row>
-    <row r="667" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="667" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A667" s="15" t="s">
         <v>4362</v>
       </c>
@@ -57921,7 +57929,7 @@
         <v/>
       </c>
     </row>
-    <row r="668" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="668" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A668" s="15" t="s">
         <v>4364</v>
       </c>
@@ -57959,7 +57967,7 @@
         <v/>
       </c>
     </row>
-    <row r="669" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="669" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A669" s="15" t="s">
         <v>4365</v>
       </c>
@@ -57997,7 +58005,7 @@
         <v/>
       </c>
     </row>
-    <row r="670" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="670" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A670" s="15" t="s">
         <v>4371</v>
       </c>
@@ -58031,7 +58039,7 @@
         <v/>
       </c>
     </row>
-    <row r="671" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="671" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A671" s="15" t="s">
         <v>4375</v>
       </c>
@@ -58067,7 +58075,7 @@
         <v/>
       </c>
     </row>
-    <row r="672" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="672" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A672" s="15" t="s">
         <v>4380</v>
       </c>
@@ -58105,7 +58113,7 @@
         <v/>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="673" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A673" s="15" t="s">
         <v>4386</v>
       </c>
@@ -58143,7 +58151,7 @@
         <v/>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="674" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A674" s="15" t="s">
         <v>4392</v>
       </c>
@@ -58177,7 +58185,7 @@
         <v/>
       </c>
     </row>
-    <row r="675" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="675" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A675" s="15" t="s">
         <v>4396</v>
       </c>
@@ -58219,7 +58227,7 @@
         <v>张世荃</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="676" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A676" s="15" t="s">
         <v>4402</v>
       </c>
@@ -58257,7 +58265,7 @@
         <v/>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="677" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A677" s="15" t="s">
         <v>4408</v>
       </c>
@@ -58295,7 +58303,7 @@
         <v/>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="678" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A678" s="15" t="s">
         <v>4413</v>
       </c>
@@ -58333,7 +58341,7 @@
         <v/>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="679" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A679" s="15" t="s">
         <v>4419</v>
       </c>
@@ -58371,7 +58379,7 @@
         <v/>
       </c>
     </row>
-    <row r="680" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="680" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A680" s="15" t="s">
         <v>4425</v>
       </c>
@@ -58405,7 +58413,7 @@
         <v/>
       </c>
     </row>
-    <row r="681" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="681" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A681" s="15" t="s">
         <v>4429</v>
       </c>
@@ -58443,7 +58451,7 @@
         <v/>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="682" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A682" s="15" t="s">
         <v>4435</v>
       </c>
@@ -58481,7 +58489,7 @@
         <v/>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="683" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A683" s="15" t="s">
         <v>4441</v>
       </c>
@@ -58519,7 +58527,7 @@
         <v/>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A684" s="15" t="s">
         <v>4447</v>
       </c>
@@ -58555,7 +58563,7 @@
         <v/>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A685" s="15" t="s">
         <v>4452</v>
       </c>
@@ -58591,7 +58599,7 @@
         <v/>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A686" s="15" t="s">
         <v>4457</v>
       </c>
@@ -58623,7 +58631,7 @@
         <v/>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A687" s="15" t="s">
         <v>4460</v>
       </c>
@@ -58655,7 +58663,7 @@
         <v/>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="688" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A688" s="15" t="s">
         <v>4463</v>
       </c>
@@ -58697,7 +58705,7 @@
         <v>刘建仁</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="689" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A689" s="15" t="s">
         <v>4469</v>
       </c>
@@ -58739,7 +58747,7 @@
         <v>张金香</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="690" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A690" s="15" t="s">
         <v>4475</v>
       </c>
@@ -58785,7 +58793,7 @@
         <v>刘丹 丁玉勇</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A691" s="15" t="s">
         <v>4483</v>
       </c>
@@ -58821,7 +58829,7 @@
         <v/>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A692" s="15" t="s">
         <v>4488</v>
       </c>
@@ -58855,7 +58863,7 @@
         <v/>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A693" s="15" t="s">
         <v>4492</v>
       </c>
@@ -58889,7 +58897,7 @@
         <v/>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A694" s="15"/>
       <c r="B694" s="6" t="s">
         <v>4496</v>
@@ -58921,7 +58929,7 @@
         <v/>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A695" s="15" t="s">
         <v>4499</v>
       </c>
@@ -58959,7 +58967,7 @@
         <v/>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="696" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A696" s="15" t="s">
         <v>4505</v>
       </c>
@@ -59006,7 +59014,7 @@
 刘友庭</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="697" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A697" s="15" t="s">
         <v>4512</v>
       </c>
@@ -59052,7 +59060,7 @@
         <v>刘娟 周羽</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A698" s="15" t="s">
         <v>4520</v>
       </c>
@@ -59086,7 +59094,7 @@
         <v/>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="699" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A699" s="15" t="s">
         <v>4524</v>
       </c>
@@ -59128,7 +59136,7 @@
         <v>刘娇娇</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="700" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A700" s="15" t="s">
         <v>4530</v>
       </c>
@@ -59176,7 +59184,7 @@
         <v>张琦 易利民</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A701" s="15" t="s">
         <v>4539</v>
       </c>
@@ -59214,7 +59222,7 @@
         <v/>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A702" s="15" t="s">
         <v>4545</v>
       </c>
@@ -59250,7 +59258,7 @@
         <v/>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A703" s="15" t="s">
         <v>4550</v>
       </c>
@@ -59288,7 +59296,7 @@
         <v/>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A704" s="15" t="s">
         <v>4556</v>
       </c>
@@ -59326,7 +59334,7 @@
         <v/>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="705" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A705" s="15" t="s">
         <v>4562</v>
       </c>
@@ -59362,7 +59370,7 @@
         <v/>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="706" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A706" s="15" t="s">
         <v>4567</v>
       </c>
@@ -59396,7 +59404,7 @@
         <v/>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="707" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A707" s="15" t="s">
         <v>4571</v>
       </c>
@@ -59438,7 +59446,7 @@
         <v>王锋</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="708" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A708" s="15" t="s">
         <v>4574</v>
       </c>
@@ -59472,7 +59480,7 @@
         <v/>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="709" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A709" s="15" t="s">
         <v>4578</v>
       </c>
@@ -59510,7 +59518,7 @@
         <v/>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="710" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A710" s="15" t="s">
         <v>4584</v>
       </c>
@@ -59544,7 +59552,7 @@
         <v/>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="711" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A711" s="15" t="s">
         <v>4588</v>
       </c>
@@ -59590,7 +59598,7 @@
         <v>黄丽 刘忠文</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="712" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A712" s="15" t="s">
         <v>4595</v>
       </c>
@@ -59636,7 +59644,7 @@
         <v>邱刚 陈筠</v>
       </c>
     </row>
-    <row r="713" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="713" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A713" s="15" t="s">
         <v>4603</v>
       </c>
@@ -59680,7 +59688,7 @@
         <v>周杰云 刘足凤</v>
       </c>
     </row>
-    <row r="714" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="714" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A714" s="15" t="s">
         <v>4611</v>
       </c>
@@ -59720,7 +59728,7 @@
         <v>万丽</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="715" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A715" s="15" t="s">
         <v>4617</v>
       </c>
@@ -59760,7 +59768,7 @@
         <v>欧阳小璇</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="716" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A716" s="15" t="s">
         <v>4623</v>
       </c>
@@ -59800,7 +59808,7 @@
         <v>周正英</v>
       </c>
     </row>
-    <row r="717" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="717" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A717" s="15" t="s">
         <v>4629</v>
       </c>
@@ -59840,7 +59848,7 @@
         <v>宋国珍</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="718" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A718" s="15" t="s">
         <v>4635</v>
       </c>
@@ -59880,7 +59888,7 @@
         <v>黄承旭</v>
       </c>
     </row>
-    <row r="719" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="719" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A719" s="15" t="s">
         <v>4641</v>
       </c>
@@ -59924,7 +59932,7 @@
         <v>夏瑶 许扬坤</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="720" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A720" s="15" t="s">
         <v>4649</v>
       </c>
@@ -59968,7 +59976,7 @@
         <v>周好英 罗秋基</v>
       </c>
     </row>
-    <row r="721" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="721" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A721" s="15" t="s">
         <v>4657</v>
       </c>
@@ -60012,7 +60020,7 @@
         <v>王淑风 胡椿之</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="722" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A722" s="15" t="s">
         <v>4665</v>
       </c>
@@ -60052,7 +60060,7 @@
         <v>曾庆铭</v>
       </c>
     </row>
-    <row r="723" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="723" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A723" s="15" t="s">
         <v>4671</v>
       </c>
@@ -60094,7 +60102,7 @@
         <v>夏天珺</v>
       </c>
     </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="724" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A724" s="15" t="s">
         <v>4677</v>
       </c>
@@ -60132,7 +60140,7 @@
         <v/>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="725" spans="1:15" ht="40.5" hidden="1" x14ac:dyDescent="0.15">
       <c r="A725" s="15" t="s">
         <v>4683</v>
       </c>
@@ -60168,7 +60176,7 @@
         <v/>
       </c>
     </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="726" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A726" s="15" t="s">
         <v>4688</v>
       </c>
@@ -60200,7 +60208,7 @@
         <v/>
       </c>
     </row>
-    <row r="727" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="727" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A727" s="15" t="s">
         <v>4691</v>
       </c>
@@ -60246,7 +60254,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="728" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="728" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A728" s="15" t="s">
         <v>4694</v>
       </c>
@@ -60292,7 +60300,7 @@
         <v>肖兰平 胡苏平</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="729" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A729" s="3" t="s">
         <v>4696</v>
       </c>
@@ -60326,7 +60334,7 @@
         <v/>
       </c>
     </row>
-    <row r="730" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="730" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A730" s="15" t="s">
         <v>4700</v>
       </c>
@@ -60366,7 +60374,7 @@
         <v/>
       </c>
     </row>
-    <row r="731" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="731" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A731" s="15" t="s">
         <v>4707</v>
       </c>
@@ -60400,7 +60408,7 @@
         <v/>
       </c>
     </row>
-    <row r="732" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="732" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A732" s="15" t="s">
         <v>4710</v>
       </c>
@@ -60434,7 +60442,7 @@
         <v/>
       </c>
     </row>
-    <row r="733" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="733" spans="1:15" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A733" s="15" t="s">
         <v>4714</v>
       </c>
@@ -60474,7 +60482,7 @@
         <v/>
       </c>
     </row>
-    <row r="734" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="734" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A734" s="15"/>
       <c r="B734" s="6" t="s">
         <v>4721</v>
@@ -60518,7 +60526,7 @@
         <v>谢世平 张开燕</v>
       </c>
     </row>
-    <row r="735" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="735" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A735" s="15" t="s">
         <v>4728</v>
       </c>
@@ -60566,7 +60574,7 @@
         <v>朱小兵 肖菊月</v>
       </c>
     </row>
-    <row r="736" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="736" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A736" s="15" t="s">
         <v>4736</v>
       </c>
@@ -60608,7 +60616,7 @@
         <v>刘秋芳</v>
       </c>
     </row>
-    <row r="737" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="737" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A737" s="15" t="s">
         <v>4742</v>
       </c>
@@ -60654,7 +60662,7 @@
         <v>王燕萍 李文军</v>
       </c>
     </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="738" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A738" s="15" t="s">
         <v>4745</v>
       </c>
@@ -60686,7 +60694,7 @@
         <v/>
       </c>
     </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="739" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A739" s="15" t="s">
         <v>4748</v>
       </c>
@@ -60722,7 +60730,7 @@
         <v/>
       </c>
     </row>
-    <row r="740" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="740" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A740" s="15" t="s">
         <v>4753</v>
       </c>
@@ -60770,7 +60778,7 @@
         <v>王青花 刘本兴</v>
       </c>
     </row>
-    <row r="741" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="741" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A741" s="15" t="s">
         <v>4756</v>
       </c>
@@ -60812,7 +60820,7 @@
         <v>龙晓萍</v>
       </c>
     </row>
-    <row r="742" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="742" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A742" s="15" t="s">
         <v>4762</v>
       </c>
@@ -60854,7 +60862,7 @@
         <v>肖雅清</v>
       </c>
     </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="743" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A743" s="15" t="s">
         <v>4768</v>
       </c>
@@ -60888,7 +60896,7 @@
         <v/>
       </c>
     </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="744" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A744" s="15" t="s">
         <v>4772</v>
       </c>
@@ -60926,7 +60934,7 @@
         <v/>
       </c>
     </row>
-    <row r="745" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="745" spans="1:15" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A745" s="15" t="s">
         <v>4778</v>
       </c>
@@ -60964,7 +60972,7 @@
         <v/>
       </c>
     </row>
-    <row r="746" spans="1:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="746" spans="1:15" ht="21.95" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A746" s="15" t="s">
         <v>4784</v>
       </c>
@@ -60998,7 +61006,7 @@
         <v/>
       </c>
     </row>
-    <row r="747" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="747" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A747" s="15" t="s">
         <v>4788</v>
       </c>
@@ -61046,7 +61054,7 @@
         <v>江世林 吴秀兰</v>
       </c>
     </row>
-    <row r="748" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="748" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A748" s="15" t="s">
         <v>4797</v>
       </c>
@@ -61088,7 +61096,7 @@
         <v>张轩铭</v>
       </c>
     </row>
-    <row r="749" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="749" spans="1:15" ht="38.1" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A749" s="15" t="s">
         <v>4803</v>
       </c>
@@ -61136,7 +61144,7 @@
         <v>刘瑛 肖海</v>
       </c>
     </row>
-    <row r="750" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="750" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A750" s="15" t="s">
         <v>4812</v>
       </c>
@@ -61182,7 +61190,7 @@
         <v>梁长征 胡冬英</v>
       </c>
     </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="751" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A751" s="15" t="s">
         <v>4816</v>
       </c>
@@ -61218,7 +61226,7 @@
         <v/>
       </c>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="752" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A752" s="15" t="s">
         <v>4821</v>
       </c>
@@ -61254,7 +61262,7 @@
         <v/>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="753" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A753" s="15" t="s">
         <v>4826</v>
       </c>
@@ -61286,7 +61294,7 @@
         <v/>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="754" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A754" s="15" t="s">
         <v>4829</v>
       </c>
@@ -61318,7 +61326,7 @@
         <v/>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="755" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A755" s="15" t="s">
         <v>4832</v>
       </c>
@@ -61350,7 +61358,7 @@
         <v/>
       </c>
     </row>
-    <row r="756" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="756" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A756" s="15" t="s">
         <v>4835</v>
       </c>
@@ -61396,7 +61404,7 @@
         <v>汪小慧 刘轶星</v>
       </c>
     </row>
-    <row r="757" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="757" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A757" s="15" t="s">
         <v>4839</v>
       </c>
@@ -61436,7 +61444,7 @@
         <v>高义茂</v>
       </c>
     </row>
-    <row r="758" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="758" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A758" s="15" t="s">
         <v>4845</v>
       </c>
@@ -61480,7 +61488,7 @@
         <v>康博文 邓燕</v>
       </c>
     </row>
-    <row r="759" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="759" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A759" s="15" t="s">
         <v>4853</v>
       </c>
@@ -61608,7 +61616,7 @@
         <v>李豫西</v>
       </c>
     </row>
-    <row r="762" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="762" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A762" s="15" t="s">
         <v>4874</v>
       </c>
@@ -61650,7 +61658,7 @@
         <v>曹新陈</v>
       </c>
     </row>
-    <row r="763" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="763" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A763" s="15" t="s">
         <v>4880</v>
       </c>
@@ -61698,7 +61706,7 @@
         <v>钱志朋 曾雪薇</v>
       </c>
     </row>
-    <row r="764" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="764" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A764" s="15" t="s">
         <v>4889</v>
       </c>
@@ -61746,7 +61754,7 @@
         <v>廖芬秀 吴富喜</v>
       </c>
     </row>
-    <row r="765" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="765" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A765" s="15" t="s">
         <v>4898</v>
       </c>
@@ -61788,7 +61796,7 @@
         <v>周小燕</v>
       </c>
     </row>
-    <row r="766" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="766" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A766" s="15" t="s">
         <v>4903</v>
       </c>
@@ -61836,7 +61844,7 @@
         <v>伍继先 胡小青</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="767" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A767" s="15" t="s">
         <v>4911</v>
       </c>
@@ -61874,7 +61882,7 @@
         <v/>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="768" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A768" s="15" t="s">
         <v>4917</v>
       </c>
@@ -61912,7 +61920,7 @@
         <v/>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="769" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A769" s="15" t="s">
         <v>4923</v>
       </c>
@@ -61946,7 +61954,7 @@
         <v/>
       </c>
     </row>
-    <row r="770" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="770" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A770" s="15" t="s">
         <v>4927</v>
       </c>
@@ -61986,7 +61994,7 @@
         <v>钟青</v>
       </c>
     </row>
-    <row r="771" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="771" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A771" s="15" t="s">
         <v>4931</v>
       </c>
@@ -62032,7 +62040,7 @@
         <v>李民 张园园</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="772" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A772" s="15" t="s">
         <v>4939</v>
       </c>
@@ -62068,7 +62076,7 @@
         <v/>
       </c>
     </row>
-    <row r="773" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="773" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A773" s="15" t="s">
         <v>4944</v>
       </c>
@@ -62114,7 +62122,7 @@
         <v>周水英 焦大保</v>
       </c>
     </row>
-    <row r="774" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="774" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A774" s="15" t="s">
         <v>4952</v>
       </c>
@@ -62156,7 +62164,7 @@
         <v>洪鑫</v>
       </c>
     </row>
-    <row r="775" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="775" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A775" s="15" t="s">
         <v>4955</v>
       </c>
@@ -62202,7 +62210,7 @@
         <v>姜伟和 龙慧</v>
       </c>
     </row>
-    <row r="776" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="776" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A776" s="15" t="s">
         <v>4963</v>
       </c>
@@ -62246,7 +62254,7 @@
         <v>黄冬鸣 裴露</v>
       </c>
     </row>
-    <row r="777" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="777" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A777" s="15" t="s">
         <v>4971</v>
       </c>
@@ -62294,7 +62302,7 @@
         <v>李志红 魏立民</v>
       </c>
     </row>
-    <row r="778" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="778" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A778" s="15" t="s">
         <v>4976</v>
       </c>
@@ -62336,7 +62344,7 @@
         <v>徐磊</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="779" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A779" s="15" t="s">
         <v>4982</v>
       </c>
@@ -62372,7 +62380,7 @@
         <v/>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="780" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A780" s="15" t="s">
         <v>4987</v>
       </c>
@@ -62404,7 +62412,7 @@
         <v/>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="781" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A781" s="15" t="s">
         <v>4990</v>
       </c>
@@ -62438,7 +62446,7 @@
         <v/>
       </c>
     </row>
-    <row r="782" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="782" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A782" s="15" t="s">
         <v>4994</v>
       </c>
@@ -62482,7 +62490,7 @@
         <v/>
       </c>
     </row>
-    <row r="783" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="783" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A783" s="15" t="s">
         <v>4995</v>
       </c>
@@ -62522,7 +62530,7 @@
         <v>曾美君</v>
       </c>
     </row>
-    <row r="784" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="784" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A784" s="15" t="s">
         <v>5001</v>
       </c>
@@ -62562,7 +62570,7 @@
         <v>蒋力</v>
       </c>
     </row>
-    <row r="785" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="785" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A785" s="15" t="s">
         <v>5007</v>
       </c>
@@ -62608,7 +62616,7 @@
         <v>李艳红 陈林</v>
       </c>
     </row>
-    <row r="786" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="786" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A786" s="15" t="s">
         <v>5016</v>
       </c>
@@ -62652,7 +62660,7 @@
         <v>钟新香 王华</v>
       </c>
     </row>
-    <row r="787" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="787" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A787" s="15" t="s">
         <v>5024</v>
       </c>
@@ -62700,7 +62708,7 @@
         <v>刘志强 王飞丽</v>
       </c>
     </row>
-    <row r="788" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="788" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A788" s="15" t="s">
         <v>5033</v>
       </c>
@@ -62744,7 +62752,7 @@
         <v>罗师凤 郭长俊</v>
       </c>
     </row>
-    <row r="789" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="789" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A789" s="15" t="s">
         <v>5041</v>
       </c>
@@ -62784,7 +62792,7 @@
         <v>胡慧</v>
       </c>
     </row>
-    <row r="790" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="790" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A790" s="15" t="s">
         <v>5047</v>
       </c>
@@ -62832,7 +62840,7 @@
         <v>肖文军 刘小丽</v>
       </c>
     </row>
-    <row r="791" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="791" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A791" s="15" t="s">
         <v>5056</v>
       </c>
@@ -62880,7 +62888,7 @@
         <v>欧阳艳凤 郭文熹</v>
       </c>
     </row>
-    <row r="792" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="792" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A792" s="15" t="s">
         <v>5065</v>
       </c>
@@ -62928,7 +62936,7 @@
         <v>胡海佩 王文明</v>
       </c>
     </row>
-    <row r="793" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="793" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A793" s="15" t="s">
         <v>5074</v>
       </c>
@@ -62970,7 +62978,7 @@
         <v>陈伟华</v>
       </c>
     </row>
-    <row r="794" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="794" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A794" s="15" t="s">
         <v>5080</v>
       </c>
@@ -63010,7 +63018,7 @@
         <v>王娜</v>
       </c>
     </row>
-    <row r="795" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="795" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A795" s="15" t="s">
         <v>5086</v>
       </c>
@@ -63050,7 +63058,7 @@
         <v>罗小芳</v>
       </c>
     </row>
-    <row r="796" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="796" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A796" s="15" t="s">
         <v>5092</v>
       </c>
@@ -63094,7 +63102,7 @@
         <v>王头法 罗根媖</v>
       </c>
     </row>
-    <row r="797" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="797" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A797" s="15" t="s">
         <v>5100</v>
       </c>
@@ -63138,7 +63146,7 @@
         <v>张六妹 胡桂成</v>
       </c>
     </row>
-    <row r="798" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="798" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A798" s="15" t="s">
         <v>5108</v>
       </c>
@@ -63176,7 +63184,7 @@
         <v/>
       </c>
     </row>
-    <row r="799" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="799" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A799" s="15" t="s">
         <v>5114</v>
       </c>
@@ -63222,7 +63230,7 @@
         <v>廖荣英 邹继华</v>
       </c>
     </row>
-    <row r="800" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="800" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A800" s="15" t="s">
         <v>5118</v>
       </c>
@@ -63260,7 +63268,7 @@
         <v/>
       </c>
     </row>
-    <row r="801" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="801" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A801" s="15" t="s">
         <v>5124</v>
       </c>
@@ -63294,7 +63302,7 @@
         <v/>
       </c>
     </row>
-    <row r="802" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="802" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A802" s="15" t="s">
         <v>5128</v>
       </c>
@@ -63332,7 +63340,7 @@
         <v/>
       </c>
     </row>
-    <row r="803" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="803" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A803" s="15" t="s">
         <v>5134</v>
       </c>
@@ -63366,7 +63374,7 @@
         <v/>
       </c>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="804" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A804" s="15" t="s">
         <v>5138</v>
       </c>
@@ -63404,7 +63412,7 @@
         <v/>
       </c>
     </row>
-    <row r="805" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="805" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A805" s="15" t="s">
         <v>5144</v>
       </c>
@@ -63442,7 +63450,7 @@
         <v/>
       </c>
     </row>
-    <row r="806" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="806" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A806" s="15" t="s">
         <v>5150</v>
       </c>
@@ -63484,7 +63492,7 @@
         <v/>
       </c>
     </row>
-    <row r="807" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="807" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A807" s="15" t="s">
         <v>5151</v>
       </c>
@@ -63522,7 +63530,7 @@
         <v/>
       </c>
     </row>
-    <row r="808" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="808" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A808" s="15" t="s">
         <v>5152</v>
       </c>
@@ -63558,7 +63566,7 @@
         <v/>
       </c>
     </row>
-    <row r="809" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="809" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A809" s="15" t="s">
         <v>5157</v>
       </c>
@@ -63604,7 +63612,7 @@
         <v>李春华 郭厚河</v>
       </c>
     </row>
-    <row r="810" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="810" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A810" s="15" t="s">
         <v>5165</v>
       </c>
@@ -63652,7 +63660,7 @@
         <v>尹嵩 姚文娟</v>
       </c>
     </row>
-    <row r="811" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="811" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A811" s="15" t="s">
         <v>5174</v>
       </c>
@@ -63700,7 +63708,7 @@
         <v>胡秋妹 张锋兴</v>
       </c>
     </row>
-    <row r="812" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="812" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A812" s="15" t="s">
         <v>5183</v>
       </c>
@@ -63742,7 +63750,7 @@
         <v>朱莎</v>
       </c>
     </row>
-    <row r="813" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="813" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A813" s="15" t="s">
         <v>5189</v>
       </c>
@@ -63782,7 +63790,7 @@
         <v>杨婧</v>
       </c>
     </row>
-    <row r="814" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="814" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A814" s="15" t="s">
         <v>5195</v>
       </c>
@@ -63822,7 +63830,7 @@
         <v>谢同峰</v>
       </c>
     </row>
-    <row r="815" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="815" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A815" s="15" t="s">
         <v>5201</v>
       </c>
@@ -63862,7 +63870,7 @@
         <v>刘倩文</v>
       </c>
     </row>
-    <row r="816" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="816" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A816" s="15" t="s">
         <v>5207</v>
       </c>
@@ -63902,7 +63910,7 @@
         <v>张秋萍</v>
       </c>
     </row>
-    <row r="817" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="817" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A817" s="15" t="s">
         <v>5213</v>
       </c>
@@ -63948,7 +63956,7 @@
         <v>罗根华 王燕华</v>
       </c>
     </row>
-    <row r="818" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="818" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A818" s="15" t="s">
         <v>5221</v>
       </c>
@@ -63996,7 +64004,7 @@
         <v>黄兵 戴智芳</v>
       </c>
     </row>
-    <row r="819" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="819" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A819" s="15" t="s">
         <v>5230</v>
       </c>
@@ -64044,7 +64052,7 @@
         <v>黄兵 戴智芳</v>
       </c>
     </row>
-    <row r="820" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="820" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A820" s="15"/>
       <c r="B820" s="6" t="s">
         <v>5231</v>
@@ -64078,7 +64086,7 @@
         <v/>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="821" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A821" s="15" t="s">
         <v>5236</v>
       </c>
@@ -64116,7 +64124,7 @@
         <v/>
       </c>
     </row>
-    <row r="822" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="822" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A822" s="15" t="s">
         <v>5242</v>
       </c>
@@ -64154,7 +64162,7 @@
         <v/>
       </c>
     </row>
-    <row r="823" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="823" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A823" s="15" t="s">
         <v>5243</v>
       </c>
@@ -64196,7 +64204,7 @@
         <v>吴雅荣</v>
       </c>
     </row>
-    <row r="824" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="824" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A824" s="15" t="s">
         <v>5249</v>
       </c>
@@ -64238,7 +64246,7 @@
         <v>翟回乡</v>
       </c>
     </row>
-    <row r="825" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="825" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A825" s="15" t="s">
         <v>5255</v>
       </c>
@@ -64286,7 +64294,7 @@
         <v>陈武 陈玉玲</v>
       </c>
     </row>
-    <row r="826" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="826" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A826" s="15" t="s">
         <v>5264</v>
       </c>
@@ -64328,7 +64336,7 @@
         <v>彭志强</v>
       </c>
     </row>
-    <row r="827" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="827" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A827" s="15" t="s">
         <v>5270</v>
       </c>
@@ -64370,7 +64378,7 @@
         <v>王秀凤</v>
       </c>
     </row>
-    <row r="828" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="828" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A828" s="15" t="s">
         <v>5276</v>
       </c>
@@ -64416,7 +64424,7 @@
         <v>陈燕 王希鹏</v>
       </c>
     </row>
-    <row r="829" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="829" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A829" s="15" t="s">
         <v>5284</v>
       </c>
@@ -64456,7 +64464,7 @@
         <v>欧阳凯松</v>
       </c>
     </row>
-    <row r="830" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="830" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A830" s="15" t="s">
         <v>5290</v>
       </c>
@@ -64504,7 +64512,7 @@
         <v>王良棵 赖琼英</v>
       </c>
     </row>
-    <row r="831" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="831" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A831" s="15" t="s">
         <v>5299</v>
       </c>
@@ -64546,7 +64554,7 @@
         <v>吴杰</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="832" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A832" s="15" t="s">
         <v>5305</v>
       </c>
@@ -64584,7 +64592,7 @@
         <v/>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="833" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A833" s="15" t="s">
         <v>5311</v>
       </c>
@@ -64622,7 +64630,7 @@
         <v/>
       </c>
     </row>
-    <row r="834" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="834" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A834" s="15" t="s">
         <v>5317</v>
       </c>
@@ -64660,7 +64668,7 @@
         <v/>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="835" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A835" s="15" t="s">
         <v>5318</v>
       </c>
@@ -64696,7 +64704,7 @@
         <v/>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="836" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A836" s="15" t="s">
         <v>5323</v>
       </c>
@@ -64734,7 +64742,7 @@
         <v/>
       </c>
     </row>
-    <row r="837" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="837" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A837" s="15" t="s">
         <v>5329</v>
       </c>
@@ -64776,7 +64784,7 @@
         <v>石建涛</v>
       </c>
     </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="838" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A838" s="15" t="s">
         <v>5335</v>
       </c>
@@ -64808,7 +64816,7 @@
         <v/>
       </c>
     </row>
-    <row r="839" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="839" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A839" s="15" t="s">
         <v>5338</v>
       </c>
@@ -64850,7 +64858,7 @@
         <v>李文杰</v>
       </c>
     </row>
-    <row r="840" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="840" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A840" s="15" t="s">
         <v>5344</v>
       </c>
@@ -64892,7 +64900,7 @@
         <v>王红勇</v>
       </c>
     </row>
-    <row r="841" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="841" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A841" s="15" t="s">
         <v>5350</v>
       </c>
@@ -64934,7 +64942,7 @@
         <v>李云</v>
       </c>
     </row>
-    <row r="842" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="842" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A842" s="15" t="s">
         <v>5356</v>
       </c>
@@ -64980,7 +64988,7 @@
         <v>刘玉梅 范孝祥</v>
       </c>
     </row>
-    <row r="843" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="843" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A843" s="15" t="s">
         <v>5364</v>
       </c>
@@ -65026,7 +65034,7 @@
         <v>晏志光 刘娟</v>
       </c>
     </row>
-    <row r="844" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="844" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A844" s="15" t="s">
         <v>5372</v>
       </c>
@@ -65068,7 +65076,7 @@
         <v>冯程</v>
       </c>
     </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="845" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A845" s="15" t="s">
         <v>5376</v>
       </c>
@@ -65106,7 +65114,7 @@
         <v/>
       </c>
     </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="846" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A846" s="15" t="s">
         <v>5382</v>
       </c>
@@ -65144,7 +65152,7 @@
         <v/>
       </c>
     </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="847" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A847" s="15" t="s">
         <v>5388</v>
       </c>
@@ -65182,7 +65190,7 @@
         <v/>
       </c>
     </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="848" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A848" s="15" t="s">
         <v>5394</v>
       </c>
@@ -65220,7 +65228,7 @@
         <v/>
       </c>
     </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="849" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A849" s="15" t="s">
         <v>5400</v>
       </c>
@@ -65258,7 +65266,7 @@
         <v/>
       </c>
     </row>
-    <row r="850" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="850" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A850" s="15" t="s">
         <v>5406</v>
       </c>
@@ -65300,7 +65308,7 @@
         <v>罗家忠</v>
       </c>
     </row>
-    <row r="851" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="851" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A851" s="15" t="s">
         <v>5412</v>
       </c>
@@ -65346,7 +65354,7 @@
         <v>胡智武 谢丹</v>
       </c>
     </row>
-    <row r="852" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="852" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A852" s="15" t="s">
         <v>5415</v>
       </c>
@@ -65392,7 +65400,7 @@
         <v>胡智武 谢丹</v>
       </c>
     </row>
-    <row r="853" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="853" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A853" s="15" t="s">
         <v>5417</v>
       </c>
@@ -65434,7 +65442,7 @@
         <v>邱华英</v>
       </c>
     </row>
-    <row r="854" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="854" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A854" s="15" t="s">
         <v>5423</v>
       </c>
@@ -65520,7 +65528,7 @@
         <v>李展搏 肖苏华</v>
       </c>
     </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="856" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A856" s="15" t="s">
         <v>5437</v>
       </c>
@@ -65554,7 +65562,7 @@
         <v/>
       </c>
     </row>
-    <row r="857" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="857" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A857" s="15" t="s">
         <v>5441</v>
       </c>
@@ -65596,7 +65604,7 @@
         <v>段娇琴</v>
       </c>
     </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="858" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A858" s="15" t="s">
         <v>5447</v>
       </c>
@@ -65634,7 +65642,7 @@
         <v/>
       </c>
     </row>
-    <row r="859" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="859" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A859" s="15" t="s">
         <v>5453</v>
       </c>
@@ -65682,7 +65690,7 @@
         <v>李丽 谢步兴</v>
       </c>
     </row>
-    <row r="860" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="860" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A860" s="15" t="s">
         <v>5462</v>
       </c>
@@ -65810,7 +65818,7 @@
         <v>王卫红</v>
       </c>
     </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="863" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A863" s="15" t="s">
         <v>5484</v>
       </c>
@@ -65850,7 +65858,7 @@
         <v/>
       </c>
     </row>
-    <row r="864" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="864" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A864" s="15" t="s">
         <v>5490</v>
       </c>
@@ -65890,7 +65898,7 @@
         <v>欧阳学海</v>
       </c>
     </row>
-    <row r="865" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="865" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A865" s="15" t="s">
         <v>5496</v>
       </c>
@@ -65934,7 +65942,7 @@
         <v>阮燕芳 赵令辉</v>
       </c>
     </row>
-    <row r="866" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="866" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A866" s="15" t="s">
         <v>5504</v>
       </c>
@@ -65980,7 +65988,7 @@
         <v>刘庆华 吴传柱</v>
       </c>
     </row>
-    <row r="867" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="867" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A867" s="15" t="s">
         <v>5513</v>
       </c>
@@ -66026,7 +66034,7 @@
         <v>陈美青 曹绍剑</v>
       </c>
     </row>
-    <row r="868" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="868" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A868" s="15" t="s">
         <v>5521</v>
       </c>
@@ -66072,7 +66080,7 @@
         <v>陈美青 曹绍剑</v>
       </c>
     </row>
-    <row r="869" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="869" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A869" s="15" t="s">
         <v>5523</v>
       </c>
@@ -66118,7 +66126,7 @@
         <v>康淑萍 刘文军</v>
       </c>
     </row>
-    <row r="870" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="870" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A870" s="15" t="s">
         <v>5531</v>
       </c>
@@ -66160,7 +66168,7 @@
         <v>刘琼</v>
       </c>
     </row>
-    <row r="871" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="871" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A871" s="15" t="s">
         <v>5536</v>
       </c>
@@ -66208,7 +66216,7 @@
         <v>彭武强 邹俊霞</v>
       </c>
     </row>
-    <row r="872" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="872" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A872" s="15" t="s">
         <v>5545</v>
       </c>
@@ -66246,7 +66254,7 @@
         <v/>
       </c>
     </row>
-    <row r="873" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="873" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A873" s="15" t="s">
         <v>5546</v>
       </c>
@@ -66286,7 +66294,7 @@
         <v/>
       </c>
     </row>
-    <row r="874" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="874" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A874" s="15" t="s">
         <v>5553</v>
       </c>
@@ -66330,7 +66338,7 @@
         <v>刘小红 王茨平</v>
       </c>
     </row>
-    <row r="875" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="875" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A875" s="15" t="s">
         <v>5561</v>
       </c>
@@ -66376,7 +66384,7 @@
         <v>王树文 马慧娥</v>
       </c>
     </row>
-    <row r="876" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="876" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A876" s="15" t="s">
         <v>5569</v>
       </c>
@@ -66414,7 +66422,7 @@
         <v/>
       </c>
     </row>
-    <row r="877" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="877" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A877" s="15" t="s">
         <v>5575</v>
       </c>
@@ -66448,7 +66456,7 @@
         <v/>
       </c>
     </row>
-    <row r="878" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="878" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A878" s="15" t="s">
         <v>5579</v>
       </c>
@@ -66486,7 +66494,7 @@
         <v/>
       </c>
     </row>
-    <row r="879" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="879" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A879" s="15" t="s">
         <v>5585</v>
       </c>
@@ -66518,7 +66526,7 @@
         <v/>
       </c>
     </row>
-    <row r="880" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="880" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A880" s="15" t="s">
         <v>5588</v>
       </c>
@@ -66550,7 +66558,7 @@
         <v/>
       </c>
     </row>
-    <row r="881" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="881" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A881" s="15" t="s">
         <v>5591</v>
       </c>
@@ -66592,7 +66600,7 @@
         <v>刘佩航</v>
       </c>
     </row>
-    <row r="882" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="882" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A882" s="15" t="s">
         <v>5597</v>
       </c>
@@ -66638,7 +66646,7 @@
         <v>彭丽 王超</v>
       </c>
     </row>
-    <row r="883" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="883" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A883" s="15" t="s">
         <v>5605</v>
       </c>
@@ -66680,7 +66688,7 @@
         <v>欧阳茜茜</v>
       </c>
     </row>
-    <row r="884" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="884" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A884" s="15" t="s">
         <v>5611</v>
       </c>
@@ -66714,7 +66722,7 @@
         <v/>
       </c>
     </row>
-    <row r="885" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="885" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A885" s="15" t="s">
         <v>5615</v>
       </c>
@@ -66752,7 +66760,7 @@
         <v/>
       </c>
     </row>
-    <row r="886" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="886" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A886" s="15" t="s">
         <v>5621</v>
       </c>
@@ -66790,7 +66798,7 @@
         <v/>
       </c>
     </row>
-    <row r="887" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="887" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A887" s="15" t="s">
         <v>5627</v>
       </c>
@@ -66824,7 +66832,7 @@
         <v/>
       </c>
     </row>
-    <row r="888" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="888" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A888" s="15" t="s">
         <v>5631</v>
       </c>
@@ -66870,7 +66878,7 @@
         <v>伍嘉欣 伍友谊</v>
       </c>
     </row>
-    <row r="889" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="889" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A889" s="15" t="s">
         <v>5639</v>
       </c>
@@ -66916,7 +66924,7 @@
         <v>肖金先 汤美兰</v>
       </c>
     </row>
-    <row r="890" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="890" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A890" s="15" t="s">
         <v>5647</v>
       </c>
@@ -66958,7 +66966,7 @@
         <v>刘兰</v>
       </c>
     </row>
-    <row r="891" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="891" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A891" s="15" t="s">
         <v>5652</v>
       </c>
@@ -67000,7 +67008,7 @@
         <v>彭四明</v>
       </c>
     </row>
-    <row r="892" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="892" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A892" s="15" t="s">
         <v>5656</v>
       </c>
@@ -67044,7 +67052,7 @@
         <v>陈莉莉 李东明</v>
       </c>
     </row>
-    <row r="893" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="893" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A893" s="15" t="s">
         <v>5664</v>
       </c>
@@ -67082,7 +67090,7 @@
         <v/>
       </c>
     </row>
-    <row r="894" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="894" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A894" s="15" t="s">
         <v>5670</v>
       </c>
@@ -67124,7 +67132,7 @@
         <v>林星鑫</v>
       </c>
     </row>
-    <row r="895" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="895" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A895" s="15" t="s">
         <v>5676</v>
       </c>
@@ -67172,7 +67180,7 @@
         <v>黎萍平 晏财轩</v>
       </c>
     </row>
-    <row r="896" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="896" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A896" s="15" t="s">
         <v>5685</v>
       </c>
@@ -67206,7 +67214,7 @@
         <v/>
       </c>
     </row>
-    <row r="897" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="897" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A897" s="15" t="s">
         <v>5689</v>
       </c>
@@ -67240,7 +67248,7 @@
         <v/>
       </c>
     </row>
-    <row r="898" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="898" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A898" s="15" t="s">
         <v>5693</v>
       </c>
@@ -67274,7 +67282,7 @@
         <v/>
       </c>
     </row>
-    <row r="899" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="899" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A899" s="15" t="s">
         <v>5697</v>
       </c>
@@ -67320,7 +67328,7 @@
         <v>陈小强 王青梅</v>
       </c>
     </row>
-    <row r="900" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="900" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A900" s="15" t="s">
         <v>5705</v>
       </c>
@@ -67366,7 +67374,7 @@
         <v>肖基森 刘小英</v>
       </c>
     </row>
-    <row r="901" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="901" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A901" s="15" t="s">
         <v>5714</v>
       </c>
@@ -67412,7 +67420,7 @@
         <v>余丽华 林永根</v>
       </c>
     </row>
-    <row r="902" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="902" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A902" s="15" t="s">
         <v>5723</v>
       </c>
@@ -67458,7 +67466,7 @@
         <v>刘金龙 杨欢</v>
       </c>
     </row>
-    <row r="903" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="903" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A903" s="15" t="s">
         <v>5730</v>
       </c>
@@ -67506,7 +67514,7 @@
         <v>刘自铮 刘美琴</v>
       </c>
     </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="904" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A904" s="15" t="s">
         <v>5739</v>
       </c>
@@ -67540,7 +67548,7 @@
         <v/>
       </c>
     </row>
-    <row r="905" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="905" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A905" s="15" t="s">
         <v>5743</v>
       </c>
@@ -67588,7 +67596,7 @@
         <v>马春香 刘懿昌</v>
       </c>
     </row>
-    <row r="906" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="906" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A906" s="15" t="s">
         <v>5752</v>
       </c>
@@ -67628,7 +67636,7 @@
         <v>王柏林</v>
       </c>
     </row>
-    <row r="907" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="907" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A907" s="15" t="s">
         <v>5758</v>
       </c>
@@ -67668,7 +67676,7 @@
         <v>王靖瑶</v>
       </c>
     </row>
-    <row r="908" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="908" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A908" s="15" t="s">
         <v>5764</v>
       </c>
@@ -67712,7 +67720,7 @@
         <v>罗玉琴 杨忠燕</v>
       </c>
     </row>
-    <row r="909" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="909" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A909" s="15" t="s">
         <v>5772</v>
       </c>
@@ -67752,7 +67760,7 @@
         <v>肖杨杰</v>
       </c>
     </row>
-    <row r="910" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="910" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A910" s="15" t="s">
         <v>5778</v>
       </c>
@@ -67796,7 +67804,7 @@
         <v>王敏 刘长生</v>
       </c>
     </row>
-    <row r="911" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="911" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A911" s="15" t="s">
         <v>5785</v>
       </c>
@@ -67836,7 +67844,7 @@
         <v>周遇平</v>
       </c>
     </row>
-    <row r="912" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="912" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A912" s="15" t="s">
         <v>5791</v>
       </c>
@@ -67874,7 +67882,7 @@
         <v/>
       </c>
     </row>
-    <row r="913" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="913" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A913" s="15" t="s">
         <v>5797</v>
       </c>
@@ -67912,7 +67920,7 @@
         <v/>
       </c>
     </row>
-    <row r="914" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="914" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A914" s="15" t="s">
         <v>5803</v>
       </c>
@@ -67944,7 +67952,7 @@
         <v/>
       </c>
     </row>
-    <row r="915" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="915" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A915" s="15" t="s">
         <v>5806</v>
       </c>
@@ -67982,7 +67990,7 @@
         <v/>
       </c>
     </row>
-    <row r="916" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="916" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A916" s="15" t="s">
         <v>5812</v>
       </c>
@@ -68020,7 +68028,7 @@
         <v/>
       </c>
     </row>
-    <row r="917" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="917" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A917" s="15" t="s">
         <v>5817</v>
       </c>
@@ -68058,7 +68066,7 @@
         <v/>
       </c>
     </row>
-    <row r="918" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="918" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A918" s="15" t="s">
         <v>5823</v>
       </c>
@@ -68096,7 +68104,7 @@
         <v/>
       </c>
     </row>
-    <row r="919" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="919" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A919" s="15" t="s">
         <v>5829</v>
       </c>
@@ -68134,7 +68142,7 @@
         <v/>
       </c>
     </row>
-    <row r="920" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="920" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A920" s="15" t="s">
         <v>5835</v>
       </c>
@@ -68172,7 +68180,7 @@
         <v/>
       </c>
     </row>
-    <row r="921" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="921" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A921" s="15" t="s">
         <v>5841</v>
       </c>
@@ -68206,7 +68214,7 @@
         <v/>
       </c>
     </row>
-    <row r="922" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="922" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A922" s="15" t="s">
         <v>5845</v>
       </c>
@@ -68248,7 +68256,7 @@
         <v>孙雅丽</v>
       </c>
     </row>
-    <row r="923" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="923" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A923" s="15" t="s">
         <v>5851</v>
       </c>
@@ -68295,7 +68303,7 @@
 刘威</v>
       </c>
     </row>
-    <row r="924" spans="1:15" ht="54" x14ac:dyDescent="0.15">
+    <row r="924" spans="1:15" ht="54" hidden="1" x14ac:dyDescent="0.15">
       <c r="A924" s="15" t="s">
         <v>5858</v>
       </c>
@@ -68343,7 +68351,7 @@
         <v>曾晓娇 刘达钴</v>
       </c>
     </row>
-    <row r="925" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="925" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A925" s="15" t="s">
         <v>5867</v>
       </c>
@@ -68375,7 +68383,7 @@
       <c r="M925" s="15"/>
       <c r="N925" s="15"/>
     </row>
-    <row r="926" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="926" spans="1:15" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A926" s="15" t="s">
         <v>5872</v>
       </c>
@@ -68405,7 +68413,7 @@
       <c r="M926" s="15"/>
       <c r="N926" s="15"/>
     </row>
-    <row r="927" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="927" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A927" s="15" t="s">
         <v>5876</v>
       </c>
@@ -68454,9 +68462,7 @@
       <c r="F928" s="15" t="s">
         <v>5885</v>
       </c>
-      <c r="G928" s="15" t="s">
-        <v>1009</v>
-      </c>
+      <c r="G928" s="15"/>
       <c r="H928" s="6" t="s">
         <v>5886</v>
       </c>
@@ -68519,7 +68525,7 @@
         <v>周静</v>
       </c>
     </row>
-    <row r="930" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="930" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A930" s="15" t="s">
         <v>5893</v>
       </c>
@@ -68557,7 +68563,7 @@
         <v/>
       </c>
     </row>
-    <row r="931" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="931" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A931" s="15" t="s">
         <v>5899</v>
       </c>
@@ -68591,7 +68597,7 @@
       <c r="M931" s="15"/>
       <c r="N931" s="15"/>
     </row>
-    <row r="932" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="932" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A932" s="15" t="s">
         <v>5905</v>
       </c>
@@ -68625,7 +68631,7 @@
       <c r="M932" s="15"/>
       <c r="N932" s="15"/>
     </row>
-    <row r="933" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="933" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A933" s="15" t="s">
         <v>5911</v>
       </c>
@@ -68653,7 +68659,7 @@
       <c r="M933" s="15"/>
       <c r="N933" s="15"/>
     </row>
-    <row r="934" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="934" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A934" s="15" t="s">
         <v>5915</v>
       </c>
@@ -68695,7 +68701,7 @@
         <v>吴梅香</v>
       </c>
     </row>
-    <row r="935" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="935" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A935" s="15" t="s">
         <v>5921</v>
       </c>
@@ -68733,7 +68739,7 @@
         <v/>
       </c>
     </row>
-    <row r="936" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="936" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A936" s="15" t="s">
         <v>5927</v>
       </c>
@@ -68771,7 +68777,7 @@
         <v/>
       </c>
     </row>
-    <row r="937" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="937" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A937" s="15" t="s">
         <v>5933</v>
       </c>
@@ -68811,7 +68817,7 @@
         <v>熊泽东</v>
       </c>
     </row>
-    <row r="938" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="938" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A938" s="15" t="s">
         <v>5939</v>
       </c>
@@ -68859,7 +68865,7 @@
         <v>周春根 罗玲</v>
       </c>
     </row>
-    <row r="939" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="939" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A939" s="15" t="s">
         <v>5948</v>
       </c>
@@ -68901,7 +68907,7 @@
         <v>吴香香</v>
       </c>
     </row>
-    <row r="940" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="940" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A940" s="15" t="s">
         <v>5954</v>
       </c>
@@ -68947,7 +68953,7 @@
         <v>李根香 陈伟</v>
       </c>
     </row>
-    <row r="941" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="941" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A941" s="15" t="s">
         <v>5961</v>
       </c>
@@ -68995,7 +69001,7 @@
         <v>曹检英 曾传蕊</v>
       </c>
     </row>
-    <row r="942" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="942" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A942" s="15" t="s">
         <v>5970</v>
       </c>
@@ -69037,7 +69043,7 @@
         <v>罗根秀</v>
       </c>
     </row>
-    <row r="943" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="943" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A943" s="15" t="s">
         <v>5976</v>
       </c>
@@ -69075,7 +69081,7 @@
         <v/>
       </c>
     </row>
-    <row r="944" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="944" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A944" s="15" t="s">
         <v>5982</v>
       </c>
@@ -69113,7 +69119,7 @@
         <v/>
       </c>
     </row>
-    <row r="945" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="945" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A945" s="15" t="s">
         <v>5988</v>
       </c>
@@ -69161,7 +69167,7 @@
         <v>刘国丰 王桂花</v>
       </c>
     </row>
-    <row r="946" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="946" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A946" s="15" t="s">
         <v>5997</v>
       </c>
@@ -69205,7 +69211,7 @@
         <v>王婷 陈柳茂</v>
       </c>
     </row>
-    <row r="947" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="947" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A947" s="15" t="s">
         <v>6004</v>
       </c>
@@ -69249,7 +69255,7 @@
         <v>黄富才 陈小艳</v>
       </c>
     </row>
-    <row r="948" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="948" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A948" s="15" t="s">
         <v>6012</v>
       </c>
@@ -69293,7 +69299,7 @@
         <v>罗艳 焦建平</v>
       </c>
     </row>
-    <row r="949" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="949" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A949" s="15" t="s">
         <v>6020</v>
       </c>
@@ -69337,7 +69343,7 @@
         <v>康康 罗兰英</v>
       </c>
     </row>
-    <row r="950" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="950" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A950" s="15" t="s">
         <v>6028</v>
       </c>
@@ -69381,7 +69387,7 @@
         <v>刘小芳 张振明</v>
       </c>
     </row>
-    <row r="951" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="951" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A951" s="15" t="s">
         <v>6035</v>
       </c>
@@ -69415,7 +69421,7 @@
         <v/>
       </c>
     </row>
-    <row r="952" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="952" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A952" s="15" t="s">
         <v>6039</v>
       </c>
@@ -69453,7 +69459,7 @@
         <v/>
       </c>
     </row>
-    <row r="953" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="953" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A953" s="15" t="s">
         <v>6045</v>
       </c>
@@ -69491,7 +69497,7 @@
         <v/>
       </c>
     </row>
-    <row r="954" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="954" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A954" s="15" t="s">
         <v>6051</v>
       </c>
@@ -69525,7 +69531,7 @@
         <v/>
       </c>
     </row>
-    <row r="955" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="955" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A955" s="15" t="s">
         <v>6055</v>
       </c>
@@ -69563,7 +69569,7 @@
         <v/>
       </c>
     </row>
-    <row r="956" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="956" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A956" s="15" t="s">
         <v>6061</v>
       </c>
@@ -69601,7 +69607,7 @@
         <v/>
       </c>
     </row>
-    <row r="957" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="957" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A957" s="15" t="s">
         <v>6067</v>
       </c>
@@ -69639,7 +69645,7 @@
         <v/>
       </c>
     </row>
-    <row r="958" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="958" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A958" s="15" t="s">
         <v>6073</v>
       </c>
@@ -69677,7 +69683,7 @@
         <v/>
       </c>
     </row>
-    <row r="959" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="959" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A959" s="15" t="s">
         <v>6079</v>
       </c>
@@ -69715,7 +69721,7 @@
         <v/>
       </c>
     </row>
-    <row r="960" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="960" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A960" s="15" t="s">
         <v>6085</v>
       </c>
@@ -69753,7 +69759,7 @@
         <v/>
       </c>
     </row>
-    <row r="961" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="961" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A961" s="15" t="s">
         <v>6091</v>
       </c>
@@ -69795,7 +69801,7 @@
         <v>孙玥澜</v>
       </c>
     </row>
-    <row r="962" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="962" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A962" s="15" t="s">
         <v>6097</v>
       </c>
@@ -69837,7 +69843,7 @@
         <v>肖利剑</v>
       </c>
     </row>
-    <row r="963" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="963" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A963" s="15" t="s">
         <v>6103</v>
       </c>
@@ -69885,7 +69891,7 @@
         <v>袁玲根 刘芳芳</v>
       </c>
     </row>
-    <row r="964" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="964" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A964" s="15" t="s">
         <v>6112</v>
       </c>
@@ -69927,7 +69933,7 @@
         <v>罗娇</v>
       </c>
     </row>
-    <row r="965" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="965" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A965" s="15" t="s">
         <v>6118</v>
       </c>
@@ -69961,7 +69967,7 @@
         <v/>
       </c>
     </row>
-    <row r="966" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="966" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A966" s="15" t="s">
         <v>6122</v>
       </c>
@@ -70003,7 +70009,7 @@
         <v>周健</v>
       </c>
     </row>
-    <row r="967" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="967" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A967" s="15" t="s">
         <v>6125</v>
       </c>
@@ -70047,7 +70053,7 @@
         <v>徐爱珍 梁传兵</v>
       </c>
     </row>
-    <row r="968" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="968" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A968" s="15" t="s">
         <v>6133</v>
       </c>
@@ -70091,7 +70097,7 @@
         <v>王凤英 彭九根</v>
       </c>
     </row>
-    <row r="969" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="969" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A969" s="15" t="s">
         <v>6141</v>
       </c>
@@ -70131,7 +70137,7 @@
         <v>刘永强</v>
       </c>
     </row>
-    <row r="970" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="970" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A970" s="15" t="s">
         <v>6147</v>
       </c>
@@ -70179,7 +70185,7 @@
         <v>匡贤缙 陆柳芬</v>
       </c>
     </row>
-    <row r="971" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="971" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A971" s="18" t="s">
         <v>6156</v>
       </c>
@@ -70223,7 +70229,7 @@
         <v>杨元福 王丹</v>
       </c>
     </row>
-    <row r="972" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="972" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A972" s="15" t="s">
         <v>6165</v>
       </c>
@@ -70267,7 +70273,7 @@
         <v>汪利红 尹艳平</v>
       </c>
     </row>
-    <row r="973" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="973" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A973" s="18" t="s">
         <v>6156</v>
       </c>
@@ -70305,7 +70311,7 @@
         <v>刘未</v>
       </c>
     </row>
-    <row r="974" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="974" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A974" s="15"/>
       <c r="B974" s="6" t="s">
         <v>6178</v>
@@ -70323,7 +70329,9 @@
         <v>6182</v>
       </c>
       <c r="G974" s="15"/>
-      <c r="H974" s="15"/>
+      <c r="H974" s="6" t="s">
+        <v>6176</v>
+      </c>
       <c r="I974" s="15"/>
       <c r="J974" s="29" t="s">
         <v>6568</v>
@@ -70341,7 +70349,7 @@
         <v/>
       </c>
     </row>
-    <row r="975" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="975" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A975" s="15" t="s">
         <v>6183</v>
       </c>
@@ -70375,7 +70383,7 @@
         <v/>
       </c>
     </row>
-    <row r="976" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="976" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
       <c r="A976" s="15" t="s">
         <v>6187</v>
       </c>
@@ -70413,7 +70421,7 @@
         <v/>
       </c>
     </row>
-    <row r="977" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="977" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A977" s="15" t="s">
         <v>6193</v>
       </c>
@@ -70461,7 +70469,7 @@
         <v>李潘兰 邓相华</v>
       </c>
     </row>
-    <row r="978" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="978" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A978" s="15" t="s">
         <v>6202</v>
       </c>
@@ -70509,7 +70517,7 @@
         <v>舒惠能 余红</v>
       </c>
     </row>
-    <row r="979" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="979" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A979" s="15" t="s">
         <v>6211</v>
       </c>
@@ -70549,7 +70557,7 @@
         <v>邓娟娟</v>
       </c>
     </row>
-    <row r="980" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="980" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A980" s="15" t="s">
         <v>6217</v>
       </c>
@@ -70597,7 +70605,7 @@
         <v>林冬梅 龙春仁</v>
       </c>
     </row>
-    <row r="981" spans="1:15" ht="27" x14ac:dyDescent="0.15">
+    <row r="981" spans="1:15" ht="27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A981" s="30" t="s">
         <v>6217</v>
       </c>
